--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="269">
   <si>
     <t>Sky Apex · Stats de las unidades</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Munición disparo guiado</t>
   </si>
   <si>
-    <t>Vida máxima por guiado sin munición</t>
-  </si>
-  <si>
     <t>Alcance del fijado</t>
   </si>
   <si>
@@ -353,16 +350,10 @@
     <t>guiado_dano</t>
   </si>
   <si>
-    <t>Cantidad fija por misión: no se recargan.</t>
+    <t>Cantidad fija por misión: no se recargan. A 0, no hay más.</t>
   </si>
   <si>
     <t>guiado_municion</t>
-  </si>
-  <si>
-    <t>Con la munición a 0 puedes seguir lanzando, pero cada uno te quita esta vida máxima hasta el final de la misión (no deja lanzar el que te la quitaría toda).</t>
-  </si>
-  <si>
-    <t>guiado_coste_vida</t>
   </si>
   <si>
     <t>Distancia máxima al blanco para cargar el guiado.</t>
@@ -1524,7 +1515,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1533,7 +1524,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1545,21 +1536,21 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1577,15 +1568,15 @@
         <v>31</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B7" s="16">
         <v>200</v>
@@ -1594,7 +1585,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>31</v>
@@ -1602,7 +1593,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1611,41 +1602,41 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B9" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B10" s="16">
         <v>2000</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B11" s="16">
         <v>0.3</v>
@@ -1654,78 +1645,78 @@
         <v>34</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B12" s="16">
         <v>800</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B13" s="16">
         <v>1.72</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B14" s="16">
         <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B15" s="16">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -1757,7 +1748,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1766,7 +1757,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1778,21 +1769,21 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1810,15 +1801,15 @@
         <v>31</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B7" s="16">
         <v>0.14</v>
@@ -1827,15 +1818,15 @@
         <v>34</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B8" s="16">
         <v>0.26</v>
@@ -1844,49 +1835,49 @@
         <v>34</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B9" s="16">
         <v>1000</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="16">
         <v>70</v>
@@ -1895,32 +1886,32 @@
         <v>36</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="16">
         <v>200</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1929,92 +1920,92 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="16">
         <v>1100</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B15" s="16">
         <v>2000</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B16" s="16">
         <v>1000</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B17" s="16">
         <v>60</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B18" s="16">
         <v>600</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B19" s="16">
         <v>5</v>
@@ -2023,15 +2014,15 @@
         <v>34</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B20" s="16">
         <v>10</v>
@@ -2040,10 +2031,10 @@
         <v>34</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -2063,7 +2054,7 @@
   <sheetPr>
     <tabColor rgb="FF7A6A5A"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2542,126 +2533,126 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C22" s="11">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="D22" s="12">
         <f>'Alientormenta'!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="12">
         <f>'Abrasanubes'!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="F22" s="12">
         <f>'Ventoscuro'!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="G22" s="12">
         <f>'Fulgor'!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C23" s="11">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="D23" s="12">
         <f>'Alientormenta'!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E23" s="12">
         <f>'Abrasanubes'!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="F23" s="12">
         <f>'Ventoscuro'!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="G23" s="12">
         <f>'Fulgor'!B23</f>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="11">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="D24" s="12">
-        <f>'Alientormenta'!B24</f>
-        <v>3</v>
-      </c>
-      <c r="E24" s="12">
-        <f>'Abrasanubes'!B24</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="12">
-        <f>'Ventoscuro'!B24</f>
-        <v>3</v>
-      </c>
-      <c r="G24" s="12">
-        <f>'Fulgor'!B24</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="B25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="11">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="D25" s="12">
+        <f>'Alientormenta'!B25</f>
+        <v>15</v>
+      </c>
+      <c r="E25" s="12">
+        <f>'Abrasanubes'!B25</f>
+        <v>15</v>
+      </c>
+      <c r="F25" s="12">
+        <f>'Ventoscuro'!B25</f>
+        <v>15</v>
+      </c>
+      <c r="G25" s="12">
+        <f>'Fulgor'!B25</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C26" s="11">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="D26" s="12">
         <f>'Alientormenta'!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E26" s="12">
         <f>'Abrasanubes'!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F26" s="12">
         <f>'Ventoscuro'!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="G26" s="12">
         <f>'Fulgor'!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2669,31 +2660,31 @@
         <v>58</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C27" s="11">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="D27" s="12">
         <f>'Alientormenta'!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="E27" s="12">
         <f>'Abrasanubes'!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="F27" s="12">
         <f>'Ventoscuro'!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="G27" s="12">
         <f>'Fulgor'!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="10" t="s">
@@ -2701,23 +2692,23 @@
       </c>
       <c r="C28" s="11">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D28" s="12">
         <f>'Alientormenta'!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="12">
         <f>'Abrasanubes'!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" s="12">
         <f>'Ventoscuro'!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G28" s="12">
         <f>'Fulgor'!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2729,90 +2720,90 @@
       </c>
       <c r="C29" s="11">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D29" s="12">
         <f>'Alientormenta'!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E29" s="12">
         <f>'Abrasanubes'!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F29" s="12">
         <f>'Ventoscuro'!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G29" s="12">
         <f>'Fulgor'!B29</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="11">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="D30" s="12">
-        <f>'Alientormenta'!B30</f>
-        <v>4</v>
-      </c>
-      <c r="E30" s="12">
-        <f>'Abrasanubes'!B30</f>
-        <v>4</v>
-      </c>
-      <c r="F30" s="12">
-        <f>'Ventoscuro'!B30</f>
-        <v>4</v>
-      </c>
-      <c r="G30" s="12">
-        <f>'Fulgor'!B30</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="11">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="D31" s="12">
+        <f>'Alientormenta'!B31</f>
+        <v>50</v>
+      </c>
+      <c r="E31" s="12">
+        <f>'Abrasanubes'!B31</f>
+        <v>50</v>
+      </c>
+      <c r="F31" s="12">
+        <f>'Ventoscuro'!B31</f>
+        <v>50</v>
+      </c>
+      <c r="G31" s="12">
+        <f>'Fulgor'!B31</f>
+        <v>50</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C32" s="11">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D32" s="12">
         <f>'Alientormenta'!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E32" s="12">
         <f>'Abrasanubes'!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F32" s="12">
         <f>'Ventoscuro'!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G32" s="12">
         <f>'Fulgor'!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2820,150 +2811,150 @@
         <v>64</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C33" s="11">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D33" s="12">
         <f>'Alientormenta'!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" s="12">
         <f>'Abrasanubes'!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F33" s="12">
         <f>'Ventoscuro'!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G33" s="12">
         <f>'Fulgor'!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" s="11">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D34" s="12">
         <f>'Alientormenta'!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="12">
         <f>'Abrasanubes'!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="F34" s="12">
         <f>'Ventoscuro'!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="G34" s="12">
         <f>'Fulgor'!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" s="11">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D35" s="12">
         <f>'Alientormenta'!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="E35" s="12">
         <f>'Abrasanubes'!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="F35" s="12">
         <f>'Ventoscuro'!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="G35" s="12">
         <f>'Fulgor'!B35</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="11">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="D36" s="12">
-        <f>'Alientormenta'!B36</f>
-        <v>5</v>
-      </c>
-      <c r="E36" s="12">
-        <f>'Abrasanubes'!B36</f>
-        <v>5</v>
-      </c>
-      <c r="F36" s="12">
-        <f>'Ventoscuro'!B36</f>
-        <v>5</v>
-      </c>
-      <c r="G36" s="12">
-        <f>'Fulgor'!B36</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="11">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="D37" s="12">
+        <f>'Alientormenta'!B37</f>
+        <v>600</v>
+      </c>
+      <c r="E37" s="12">
+        <f>'Abrasanubes'!B37</f>
+        <v>600</v>
+      </c>
+      <c r="F37" s="12">
+        <f>'Ventoscuro'!B37</f>
+        <v>600</v>
+      </c>
+      <c r="G37" s="12">
+        <f>'Fulgor'!B37</f>
+        <v>600</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="C38" s="11">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="D38" s="12">
         <f>'Alientormenta'!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E38" s="12">
         <f>'Abrasanubes'!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F38" s="12">
         <f>'Ventoscuro'!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="G38" s="12">
         <f>'Fulgor'!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2971,27 +2962,27 @@
         <v>74</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C39" s="11">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D39" s="12">
         <f>'Alientormenta'!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E39" s="12">
         <f>'Abrasanubes'!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="F39" s="12">
         <f>'Ventoscuro'!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="G39" s="12">
         <f>'Fulgor'!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3003,23 +2994,23 @@
       </c>
       <c r="C40" s="11">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D40" s="12">
         <f>'Alientormenta'!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" s="12">
         <f>'Abrasanubes'!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F40" s="12">
         <f>'Ventoscuro'!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G40" s="12">
         <f>'Fulgor'!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3031,23 +3022,23 @@
       </c>
       <c r="C41" s="11">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" s="12">
         <f>'Alientormenta'!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="12">
         <f>'Abrasanubes'!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" s="12">
         <f>'Ventoscuro'!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="12">
         <f>'Fulgor'!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3055,7 +3046,7 @@
         <v>77</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C42" s="11">
         <f>Base!B42</f>
@@ -3083,54 +3074,26 @@
         <v>78</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C43" s="11">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="D43" s="12">
         <f>'Alientormenta'!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="E43" s="12">
         <f>'Abrasanubes'!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="F43" s="12">
         <f>'Ventoscuro'!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="G43" s="12">
         <f>'Fulgor'!B43</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="11">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="D44" s="12">
-        <f>'Alientormenta'!B44</f>
-        <v>110</v>
-      </c>
-      <c r="E44" s="12">
-        <f>'Abrasanubes'!B44</f>
-        <v>110</v>
-      </c>
-      <c r="F44" s="12">
-        <f>'Ventoscuro'!B44</f>
-        <v>110</v>
-      </c>
-      <c r="G44" s="12">
-        <f>'Fulgor'!B44</f>
         <v>110</v>
       </c>
     </row>
@@ -3141,11 +3104,11 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:G44">
+  <conditionalFormatting sqref="D5:G43">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(ISNUMBER($C5),D5&lt;&gt;$C5)</formula>
     </cfRule>
@@ -3160,7 +3123,7 @@
   <sheetPr>
     <tabColor rgb="FFF2B84B"/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3181,7 +3144,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3193,16 +3156,16 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3225,10 +3188,10 @@
         <v>31</v>
       </c>
       <c r="D6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3242,10 +3205,10 @@
         <v>31</v>
       </c>
       <c r="D7" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="18" t="s">
         <v>86</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3259,10 +3222,10 @@
         <v>34</v>
       </c>
       <c r="D8" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3276,10 +3239,10 @@
         <v>36</v>
       </c>
       <c r="D9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -3293,10 +3256,10 @@
         <v>38</v>
       </c>
       <c r="D10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="18" t="s">
         <v>92</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3310,10 +3273,10 @@
         <v>34</v>
       </c>
       <c r="D11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3327,10 +3290,10 @@
         <v>38</v>
       </c>
       <c r="D12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3353,10 +3316,10 @@
         <v>31</v>
       </c>
       <c r="D14" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3370,10 +3333,10 @@
         <v>44</v>
       </c>
       <c r="D15" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3387,10 +3350,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>102</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -3404,10 +3367,10 @@
         <v>34</v>
       </c>
       <c r="D17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3421,10 +3384,10 @@
         <v>48</v>
       </c>
       <c r="D18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>106</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3447,10 +3410,10 @@
         <v>31</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -3464,87 +3427,87 @@
         <v>44</v>
       </c>
       <c r="D21" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="18" t="s">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="16">
+        <v>3000</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="16">
-        <v>15</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="17" t="s">
+      <c r="E22" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="16">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D23" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="18" t="s">
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="16">
+        <v>15</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="16">
-        <v>3</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="17" t="s">
+      <c r="E25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="16">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -3552,33 +3515,33 @@
         <v>58</v>
       </c>
       <c r="B27" s="16">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D27" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3586,59 +3549,59 @@
         <v>60</v>
       </c>
       <c r="B29" s="16">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="18" t="s">
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="16">
+        <v>50</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="16">
-        <v>4</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="17" t="s">
+      <c r="E31" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B32" s="16">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D32" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3646,93 +3609,93 @@
         <v>64</v>
       </c>
       <c r="B33" s="16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D33" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="16">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="16">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="E35" s="18" t="s">
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="16">
+        <v>600</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="17" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="16">
-        <v>5</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="17" t="s">
+      <c r="E37" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="16">
+        <v>1000</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="16">
-        <v>600</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="D38" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3740,16 +3703,16 @@
         <v>74</v>
       </c>
       <c r="B39" s="16">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D39" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>140</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3757,16 +3720,16 @@
         <v>75</v>
       </c>
       <c r="B40" s="16">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="18" t="s">
         <v>142</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3774,16 +3737,16 @@
         <v>76</v>
       </c>
       <c r="B41" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="18" t="s">
         <v>144</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3794,13 +3757,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D42" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3808,33 +3771,16 @@
         <v>78</v>
       </c>
       <c r="B43" s="16">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D43" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" s="18" t="s">
         <v>148</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="16">
-        <v>110</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3844,9 +3790,9 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3858,7 +3804,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3883,7 +3829,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3897,7 +3843,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
@@ -3906,13 +3852,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3946,10 +3892,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3972,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>86</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3998,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4024,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4050,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>92</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4076,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4102,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4139,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4165,10 +4111,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4191,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>102</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4217,10 +4163,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4243,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>106</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4280,10 +4226,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4306,100 +4252,100 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="19">
         <f>IF(D22=0,"",B22/D22-1)</f>
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="18" t="s">
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="16">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="10">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="E25" s="19">
+        <f>IF(D25=0,"",B25/D25-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="16">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="10">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="E24" s="19">
-        <f>IF(D24=0,"",B24/D24-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="17" t="s">
+      <c r="G25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
@@ -4407,24 +4353,24 @@
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E26" s="19">
         <f>IF(D26=0,"",B26/D26-1)</f>
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -4433,50 +4379,50 @@
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="E27" s="19">
         <f>IF(D27=0,"",B27/D27-1)</f>
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="18" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="19">
         <f>IF(D28=0,"",B28/D28-1)</f>
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -4485,62 +4431,62 @@
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E29" s="19">
         <f>IF(D29=0,"",B29/D29-1)</f>
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G29" s="18" t="s">
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="16">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="10">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="E31" s="19">
+        <f>IF(D31=0,"",B31/D31-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="16">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="10">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="E30" s="19">
-        <f>IF(D30=0,"",B30/D30-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="17" t="s">
+      <c r="G31" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
@@ -4548,24 +4494,24 @@
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E32" s="19">
         <f>IF(D32=0,"",B32/D32-1)</f>
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -4574,139 +4520,139 @@
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" s="19">
         <f>IF(D33=0,"",B33/D33-1)</f>
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="19">
         <f>IF(D34=0,"",B34/D34-1)</f>
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="E35" s="19">
         <f>IF(D35=0,"",B35/D35-1)</f>
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="18" t="s">
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="16">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="10">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="E37" s="19">
+        <f>IF(D37=0,"",B37/D37-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="16">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="10">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="E36" s="19">
-        <f>IF(D36=0,"",B36/D36-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="17" t="s">
+      <c r="G37" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E38" s="19">
         <f>IF(D38=0,"",B38/D38-1)</f>
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -4715,24 +4661,24 @@
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E39" s="19">
         <f>IF(D39=0,"",B39/D39-1)</f>
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="18" t="s">
         <v>140</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -4741,24 +4687,24 @@
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" s="19">
         <f>IF(D40=0,"",B40/D40-1)</f>
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="18" t="s">
         <v>142</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -4767,24 +4713,24 @@
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="19">
         <f>IF(D41=0,"",B41/D41-1)</f>
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="18" t="s">
         <v>144</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -4796,7 +4742,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -4807,10 +4753,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -4819,50 +4765,24 @@
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="E43" s="19">
         <f>IF(D43=0,"",B43/D43-1)</f>
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="18" t="s">
         <v>148</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="16">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="10">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="E44" s="19">
-        <f>IF(D44=0,"",B44/D44-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4872,11 +4792,11 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B44">
+  <conditionalFormatting sqref="B5:B43">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -4891,7 +4811,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4916,7 +4836,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -4930,7 +4850,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
@@ -4939,13 +4859,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4979,10 +4899,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5005,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>86</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5031,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5057,10 +4977,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5083,10 +5003,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>92</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5109,10 +5029,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5135,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5172,10 +5092,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5198,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5224,10 +5144,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>102</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5250,10 +5170,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5276,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>106</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5313,10 +5233,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5339,100 +5259,100 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="19">
         <f>IF(D22=0,"",B22/D22-1)</f>
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="18" t="s">
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="16">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="10">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="E25" s="19">
+        <f>IF(D25=0,"",B25/D25-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="16">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="10">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="E24" s="19">
-        <f>IF(D24=0,"",B24/D24-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="17" t="s">
+      <c r="G25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
@@ -5440,24 +5360,24 @@
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E26" s="19">
         <f>IF(D26=0,"",B26/D26-1)</f>
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5466,50 +5386,50 @@
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="E27" s="19">
         <f>IF(D27=0,"",B27/D27-1)</f>
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="18" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="19">
         <f>IF(D28=0,"",B28/D28-1)</f>
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5518,62 +5438,62 @@
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E29" s="19">
         <f>IF(D29=0,"",B29/D29-1)</f>
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G29" s="18" t="s">
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="16">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="10">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="E31" s="19">
+        <f>IF(D31=0,"",B31/D31-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="16">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="10">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="E30" s="19">
-        <f>IF(D30=0,"",B30/D30-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="17" t="s">
+      <c r="G31" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
@@ -5581,24 +5501,24 @@
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E32" s="19">
         <f>IF(D32=0,"",B32/D32-1)</f>
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5607,139 +5527,139 @@
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" s="19">
         <f>IF(D33=0,"",B33/D33-1)</f>
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="19">
         <f>IF(D34=0,"",B34/D34-1)</f>
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="E35" s="19">
         <f>IF(D35=0,"",B35/D35-1)</f>
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="18" t="s">
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="16">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="10">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="E37" s="19">
+        <f>IF(D37=0,"",B37/D37-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="16">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="10">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="E36" s="19">
-        <f>IF(D36=0,"",B36/D36-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="17" t="s">
+      <c r="G37" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E38" s="19">
         <f>IF(D38=0,"",B38/D38-1)</f>
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -5748,24 +5668,24 @@
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E39" s="19">
         <f>IF(D39=0,"",B39/D39-1)</f>
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="18" t="s">
         <v>140</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -5774,24 +5694,24 @@
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" s="19">
         <f>IF(D40=0,"",B40/D40-1)</f>
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="18" t="s">
         <v>142</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -5800,24 +5720,24 @@
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="19">
         <f>IF(D41=0,"",B41/D41-1)</f>
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="18" t="s">
         <v>144</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -5829,7 +5749,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -5840,10 +5760,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -5852,50 +5772,24 @@
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="E43" s="19">
         <f>IF(D43=0,"",B43/D43-1)</f>
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="18" t="s">
         <v>148</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="16">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="10">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="E44" s="19">
-        <f>IF(D44=0,"",B44/D44-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5905,11 +5799,11 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B44">
+  <conditionalFormatting sqref="B5:B43">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -5924,7 +5818,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -5949,7 +5843,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5963,7 +5857,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
@@ -5972,13 +5866,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6012,10 +5906,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6038,10 +5932,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>86</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6064,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6090,10 +5984,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6116,10 +6010,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>92</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6142,10 +6036,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6168,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6205,10 +6099,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6231,10 +6125,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6257,10 +6151,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>102</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6283,10 +6177,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6309,10 +6203,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>106</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6346,10 +6240,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6372,100 +6266,100 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="19">
         <f>IF(D22=0,"",B22/D22-1)</f>
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="18" t="s">
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="16">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="10">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="E25" s="19">
+        <f>IF(D25=0,"",B25/D25-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="16">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="10">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="E24" s="19">
-        <f>IF(D24=0,"",B24/D24-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="17" t="s">
+      <c r="G25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
@@ -6473,24 +6367,24 @@
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E26" s="19">
         <f>IF(D26=0,"",B26/D26-1)</f>
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -6499,50 +6393,50 @@
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="E27" s="19">
         <f>IF(D27=0,"",B27/D27-1)</f>
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="18" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="19">
         <f>IF(D28=0,"",B28/D28-1)</f>
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,62 +6445,62 @@
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E29" s="19">
         <f>IF(D29=0,"",B29/D29-1)</f>
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G29" s="18" t="s">
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="16">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="10">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="E31" s="19">
+        <f>IF(D31=0,"",B31/D31-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="16">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="10">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="E30" s="19">
-        <f>IF(D30=0,"",B30/D30-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="17" t="s">
+      <c r="G31" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
@@ -6614,24 +6508,24 @@
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E32" s="19">
         <f>IF(D32=0,"",B32/D32-1)</f>
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -6640,139 +6534,139 @@
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" s="19">
         <f>IF(D33=0,"",B33/D33-1)</f>
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="19">
         <f>IF(D34=0,"",B34/D34-1)</f>
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="E35" s="19">
         <f>IF(D35=0,"",B35/D35-1)</f>
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="18" t="s">
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="16">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="10">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="E37" s="19">
+        <f>IF(D37=0,"",B37/D37-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="16">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="10">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="E36" s="19">
-        <f>IF(D36=0,"",B36/D36-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="17" t="s">
+      <c r="G37" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E38" s="19">
         <f>IF(D38=0,"",B38/D38-1)</f>
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,24 +6675,24 @@
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E39" s="19">
         <f>IF(D39=0,"",B39/D39-1)</f>
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="18" t="s">
         <v>140</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -6807,24 +6701,24 @@
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" s="19">
         <f>IF(D40=0,"",B40/D40-1)</f>
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="18" t="s">
         <v>142</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -6833,24 +6727,24 @@
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="19">
         <f>IF(D41=0,"",B41/D41-1)</f>
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="18" t="s">
         <v>144</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -6862,7 +6756,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -6873,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -6885,50 +6779,24 @@
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="E43" s="19">
         <f>IF(D43=0,"",B43/D43-1)</f>
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="18" t="s">
         <v>148</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="16">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="10">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="E44" s="19">
-        <f>IF(D44=0,"",B44/D44-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -6938,11 +6806,11 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B44">
+  <conditionalFormatting sqref="B5:B43">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -6957,7 +6825,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -6982,7 +6850,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -6996,7 +6864,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
@@ -7005,13 +6873,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7045,10 +6913,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7071,10 +6939,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>86</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7097,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7123,10 +6991,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,10 +7017,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>92</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7175,10 +7043,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7201,10 +7069,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7238,10 +7106,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7264,10 +7132,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7290,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>102</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7316,10 +7184,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7342,10 +7210,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>106</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7379,10 +7247,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7405,100 +7273,100 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="19">
         <f>IF(D22=0,"",B22/D22-1)</f>
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="18" t="s">
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="16">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="10">
+        <f>Base!B25</f>
+        <v>15</v>
+      </c>
+      <c r="E25" s="19">
+        <f>IF(D25=0,"",B25/D25-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="16">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="10">
-        <f>Base!B24</f>
-        <v>3</v>
-      </c>
-      <c r="E24" s="19">
-        <f>IF(D24=0,"",B24/D24-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="17" t="s">
+      <c r="G25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
@@ -7506,24 +7374,24 @@
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E26" s="19">
         <f>IF(D26=0,"",B26/D26-1)</f>
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -7532,50 +7400,50 @@
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="E27" s="19">
         <f>IF(D27=0,"",B27/D27-1)</f>
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="18" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="19">
         <f>IF(D28=0,"",B28/D28-1)</f>
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -7584,62 +7452,62 @@
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E29" s="19">
         <f>IF(D29=0,"",B29/D29-1)</f>
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G29" s="18" t="s">
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="16">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="10">
+        <f>Base!B31</f>
+        <v>50</v>
+      </c>
+      <c r="E31" s="19">
+        <f>IF(D31=0,"",B31/D31-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="16">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="10">
-        <f>Base!B30</f>
-        <v>4</v>
-      </c>
-      <c r="E30" s="19">
-        <f>IF(D30=0,"",B30/D30-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="17" t="s">
+      <c r="G31" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
@@ -7647,24 +7515,24 @@
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E32" s="19">
         <f>IF(D32=0,"",B32/D32-1)</f>
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -7673,139 +7541,139 @@
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" s="19">
         <f>IF(D33=0,"",B33/D33-1)</f>
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="19">
         <f>IF(D34=0,"",B34/D34-1)</f>
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="E35" s="19">
         <f>IF(D35=0,"",B35/D35-1)</f>
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="18" t="s">
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="16">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="10">
+        <f>Base!B37</f>
+        <v>600</v>
+      </c>
+      <c r="E37" s="19">
+        <f>IF(D37=0,"",B37/D37-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="16">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="10">
-        <f>Base!B36</f>
-        <v>5</v>
-      </c>
-      <c r="E36" s="19">
-        <f>IF(D36=0,"",B36/D36-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="17" t="s">
+      <c r="G37" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E38" s="19">
         <f>IF(D38=0,"",B38/D38-1)</f>
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -7814,24 +7682,24 @@
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E39" s="19">
         <f>IF(D39=0,"",B39/D39-1)</f>
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="18" t="s">
         <v>140</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -7840,24 +7708,24 @@
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" s="19">
         <f>IF(D40=0,"",B40/D40-1)</f>
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="18" t="s">
         <v>142</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -7866,24 +7734,24 @@
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="19">
         <f>IF(D41=0,"",B41/D41-1)</f>
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="18" t="s">
         <v>144</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -7895,7 +7763,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -7906,10 +7774,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -7918,50 +7786,24 @@
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="E43" s="19">
         <f>IF(D43=0,"",B43/D43-1)</f>
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="18" t="s">
         <v>148</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="16">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="10">
-        <f>Base!B44</f>
-        <v>110</v>
-      </c>
-      <c r="E44" s="19">
-        <f>IF(D44=0,"",B44/D44-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -7971,11 +7813,11 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B44">
+  <conditionalFormatting sqref="B5:B43">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -8002,7 +7844,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8011,7 +7853,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -8023,21 +7865,21 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -8049,72 +7891,72 @@
         <v>30</v>
       </c>
       <c r="B6" s="16">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="16">
+        <v>500</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="16">
-        <v>550</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="D7" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B8" s="16">
         <v>2000</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B9" s="16">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B10" s="16">
         <v>300</v>
@@ -8123,7 +7965,7 @@
         <v>31</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>31</v>
@@ -8131,7 +7973,7 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -8140,41 +7982,41 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B12" s="16">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B13" s="16">
         <v>1000</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B14" s="16">
         <v>1.7</v>
@@ -8183,15 +8025,15 @@
         <v>34</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B15" s="16">
         <v>2.9</v>
@@ -8200,32 +8042,32 @@
         <v>34</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B16" s="16">
         <v>2.2</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -8234,24 +8076,24 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B18" s="16">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="16">
         <v>4</v>
@@ -8260,49 +8102,49 @@
         <v>34</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B20" s="16">
         <v>500</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B21" s="16">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B22" s="16">
         <v>60</v>
@@ -8311,15 +8153,15 @@
         <v>34</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B23" s="16">
         <v>20</v>
@@ -8328,49 +8170,49 @@
         <v>34</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B24" s="16">
         <v>1152</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" s="16">
+        <v>30</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>193</v>
-      </c>
-      <c r="B25" s="16">
-        <v>40</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -8379,7 +8221,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B27" s="16">
         <v>25</v>
@@ -8388,15 +8230,15 @@
         <v>31</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B28" s="16">
         <v>50</v>
@@ -8405,10 +8247,10 @@
         <v>31</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -8442,7 +8284,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8451,7 +8293,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -8463,21 +8305,21 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -8495,15 +8337,15 @@
         <v>31</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B7" s="16">
         <v>100</v>
@@ -8512,7 +8354,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>31</v>
@@ -8520,24 +8362,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -8546,7 +8388,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B10" s="16">
         <v>3</v>
@@ -8555,32 +8397,32 @@
         <v>31</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B11" s="16">
         <v>1500</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B12" s="16">
         <v>5</v>
@@ -8589,15 +8431,15 @@
         <v>44</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B13" s="16">
         <v>0.12</v>
@@ -8606,15 +8448,15 @@
         <v>34</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B14" s="16">
         <v>2.2</v>
@@ -8623,15 +8465,15 @@
         <v>34</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B15" s="16">
         <v>3.6</v>
@@ -8640,44 +8482,44 @@
         <v>34</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B16" s="16">
         <v>1100</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B17" s="16">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="279">
   <si>
     <t>Sky Apex · Stats de las unidades</t>
   </si>
@@ -296,7 +296,7 @@
     <t>armadura_regen</t>
   </si>
   <si>
-    <t>Cargas del escudo (F) al empezar; también es el máximo.</t>
+    <t>Cargas del escudo (R) al empezar; también es el máximo.</t>
   </si>
   <si>
     <t>escudos</t>
@@ -491,6 +491,9 @@
     <t>velocidad</t>
   </si>
   <si>
+    <t>El del giro más cerrado a su velocidad máxima: cuanto más grande, más abiertos sus giros. Si es mayor que el tuyo (Base: 110 m), al perseguirlo puedes cerrar el giro y apuntarle (v26: 130; antes, unos 104 m).</t>
+  </si>
+  <si>
     <t>Distancia de detección</t>
   </si>
   <si>
@@ -507,6 +510,33 @@
   </si>
   <si>
     <t>Puntos al derribarlo</t>
+  </si>
+  <si>
+    <t>Huida (cuando le persigues)</t>
+  </si>
+  <si>
+    <t>Distancia a la que se siente perseguido</t>
+  </si>
+  <si>
+    <t>Con el jugador detrás, apuntándole y más cerca que esto, huye hacia delante con maniobras amplias (eses, curvas abiertas, tirabuzón, subidas y picados).</t>
+  </si>
+  <si>
+    <t>huida_distancia</t>
+  </si>
+  <si>
+    <t>Tiempo de huida (mínimo)</t>
+  </si>
+  <si>
+    <t>Pasado este tiempo (entre el mínimo y el máximo) da la vuelta con una curva abierta y vuelve a atacar.</t>
+  </si>
+  <si>
+    <t>huida_min</t>
+  </si>
+  <si>
+    <t>Tiempo de huida (máximo)</t>
+  </si>
+  <si>
+    <t>huida_max</t>
   </si>
   <si>
     <t>Bola de fuego</t>
@@ -1515,7 +1545,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1550,7 +1580,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1576,7 +1606,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B7" s="16">
         <v>200</v>
@@ -1593,7 +1623,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1602,7 +1632,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B9" s="16">
         <v>1</v>
@@ -1614,12 +1644,12 @@
         <v>154</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B10" s="16">
         <v>2000</v>
@@ -1631,12 +1661,12 @@
         <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B11" s="16">
         <v>0.3</v>
@@ -1645,78 +1675,78 @@
         <v>34</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B12" s="16">
         <v>800</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B13" s="16">
         <v>1.72</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B14" s="16">
         <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B15" s="16">
         <v>50</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -1748,7 +1778,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1757,7 +1787,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1783,7 +1813,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1809,7 +1839,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B7" s="16">
         <v>0.14</v>
@@ -1821,12 +1851,12 @@
         <v>154</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="B8" s="16">
         <v>0.26</v>
@@ -1838,12 +1868,12 @@
         <v>154</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B9" s="16">
         <v>1000</v>
@@ -1855,24 +1885,24 @@
         <v>154</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1886,7 +1916,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>116</v>
@@ -1911,7 +1941,7 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1929,7 +1959,7 @@
         <v>72</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>136</v>
@@ -1937,7 +1967,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B15" s="16">
         <v>2000</v>
@@ -1946,15 +1976,15 @@
         <v>53</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B16" s="16">
         <v>1000</v>
@@ -1963,15 +1993,15 @@
         <v>53</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B17" s="16">
         <v>60</v>
@@ -1980,15 +2010,15 @@
         <v>69</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B18" s="16">
         <v>600</v>
@@ -1997,15 +2027,15 @@
         <v>53</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B19" s="16">
         <v>5</v>
@@ -2017,12 +2047,12 @@
         <v>154</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B20" s="16">
         <v>10</v>
@@ -2034,7 +2064,7 @@
         <v>154</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -7832,7 +7862,7 @@
   <sheetPr>
     <tabColor rgb="FF5A6E8A"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -7922,121 +7952,121 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="B8" s="16">
-        <v>2000</v>
+        <v>130</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B9" s="16">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="16">
-        <v>300</v>
+        <v>3500</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="16">
+        <v>300</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="D11" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="16">
-        <v>10</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" s="18" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>165</v>
-      </c>
       <c r="B13" s="16">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E13" s="18" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="13" t="s">
         <v>167</v>
       </c>
       <c r="B14" s="16">
-        <v>1.7</v>
+        <v>10</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>169</v>
+      <c r="A15" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="B15" s="16">
-        <v>2.9</v>
+        <v>18</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>34</v>
@@ -8045,44 +8075,44 @@
         <v>154</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="16">
-        <v>2.2</v>
-      </c>
-      <c r="C16" s="10" t="s">
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="16">
+        <v>10</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="E17" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>175</v>
       </c>
       <c r="B18" s="16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>154</v>
@@ -8093,16 +8123,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="B19" s="16">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>178</v>
@@ -8113,10 +8143,10 @@
         <v>179</v>
       </c>
       <c r="B20" s="16">
-        <v>500</v>
+        <v>2.9</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>154</v>
@@ -8130,137 +8160,215 @@
         <v>181</v>
       </c>
       <c r="B21" s="16">
-        <v>2000</v>
+        <v>2.2</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>53</v>
+        <v>182</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B22" s="16">
-        <v>60</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" s="18" t="s">
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>184</v>
       </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>185</v>
       </c>
       <c r="B23" s="16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D23" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>186</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="16">
+        <v>4</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>188</v>
-      </c>
-      <c r="B24" s="16">
-        <v>1152</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="16">
+        <v>500</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="16">
-        <v>30</v>
-      </c>
-      <c r="C25" s="10" t="s">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="B26" s="16">
+        <v>2000</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B27" s="16">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="16">
+        <v>20</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B28" s="16">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B29" s="16">
+        <v>1152</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30" s="16">
+        <v>30</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" s="16">
+        <v>25</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" s="16">
         <v>50</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C33" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D33" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>198</v>
+      <c r="E33" s="18" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -8284,7 +8392,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8319,7 +8427,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -8345,7 +8453,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B7" s="16">
         <v>100</v>
@@ -8362,24 +8470,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -8388,7 +8496,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B10" s="16">
         <v>3</v>
@@ -8400,12 +8508,12 @@
         <v>154</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B11" s="16">
         <v>1500</v>
@@ -8417,12 +8525,12 @@
         <v>154</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B12" s="16">
         <v>5</v>
@@ -8434,12 +8542,12 @@
         <v>154</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B13" s="16">
         <v>0.12</v>
@@ -8451,12 +8559,12 @@
         <v>154</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B14" s="16">
         <v>2.2</v>
@@ -8468,12 +8576,12 @@
         <v>154</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B15" s="16">
         <v>3.6</v>
@@ -8485,41 +8593,41 @@
         <v>154</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B16" s="16">
         <v>1100</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B17" s="16">
         <v>2</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>154</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -14,14 +14,19 @@
     <sheet sheetId="8" name="Dragón enemigo" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Torre" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Dirigible" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Lance (aliado)" state="visible" r:id="rId14"/>
+    <sheet sheetId="11" name="Artillería" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Batallón" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Barco naval" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Superdirigible" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Sierpe" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Lance (aliado)" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="403">
   <si>
     <t>Sky Apex · Stats de las unidades</t>
   </si>
@@ -50,6 +55,9 @@
     <t>• Dragón enemigo, Torre, Dirigible y Lance (aliado): sus valores de ahora, pendientes de rediseñar.</t>
   </si>
   <si>
+    <t>• Artillería, Batallón, Barco naval, Superdirigible y Sierpe (v29): los enemigos nuevos, con valores provisionales para ajustarlos en la galería de enemigos.</t>
+  </si>
+  <si>
     <t>• En gris: ajustes que no estaban en la lista de stats; tienen los valores que ya usaba el juego.</t>
   </si>
   <si>
@@ -422,7 +430,7 @@
     <t>rayo_recarga</t>
   </si>
   <si>
-    <t>Por cada dragón, torre o dirigible que destruyes tú (no Lance).</t>
+    <t>Por cada dragón, torre, dirigible u otra unidad enemiga que destruyes tú (no Lance; los soldados sueltos no cuentan, el batallón entero sí).</t>
   </si>
   <si>
     <t>rayo_por_derribo</t>
@@ -773,6 +781,381 @@
     <t>muerto_vertical</t>
   </si>
   <si>
+    <t>Artillería</t>
+  </si>
+  <si>
+    <t>Nueva (v29): balistas, catapultas y cañones, la defensa terrestre móvil. Valores provisionales.</t>
+  </si>
+  <si>
+    <t>Balista, catapulta y cañón son iguales: solo cambia el aspecto (y el aspecto del proyectil).</t>
+  </si>
+  <si>
+    <t>Tamaño y movimiento</t>
+  </si>
+  <si>
+    <t>Largo</t>
+  </si>
+  <si>
+    <t>Tamaño en el juego: los tres modelos se escalan a este largo.</t>
+  </si>
+  <si>
+    <t>largo</t>
+  </si>
+  <si>
+    <t>Velocidad</t>
+  </si>
+  <si>
+    <t>Unidad de tierra lenta. Aún sin uso: en la galería están quietas (llegará con las misiones).</t>
+  </si>
+  <si>
+    <t>Disparo (muy de vez en cuando)</t>
+  </si>
+  <si>
+    <t>Anecdótico: en las misiones su papel será atacar a las unidades de tierra aliadas.</t>
+  </si>
+  <si>
+    <t>Pausa entre disparos (mínima)</t>
+  </si>
+  <si>
+    <t>pausa_min</t>
+  </si>
+  <si>
+    <t>Pausa entre disparos (máxima)</t>
+  </si>
+  <si>
+    <t>pausa_max</t>
+  </si>
+  <si>
+    <t>Con parábola: la gravedad lo hace caer (apuntan con adelanto).</t>
+  </si>
+  <si>
+    <t>Batallón</t>
+  </si>
+  <si>
+    <t>Nueva (v29): bloques de soldados, el objetivo de la llamarada a ras de tierra. Valores provisionales.</t>
+  </si>
+  <si>
+    <t>Soldados</t>
+  </si>
+  <si>
+    <t>Soldados por batallón (mínimo)</t>
+  </si>
+  <si>
+    <t>soldados</t>
+  </si>
+  <si>
+    <t>Cada bloque sale con un número al azar entre el mínimo y el máximo (la receta puede fijarlo).</t>
+  </si>
+  <si>
+    <t>soldados_min</t>
+  </si>
+  <si>
+    <t>Soldados por batallón (máximo)</t>
+  </si>
+  <si>
+    <t>soldados_max</t>
+  </si>
+  <si>
+    <t>Separación entre soldados</t>
+  </si>
+  <si>
+    <t>En la formación rectangular. Se nota al empezar otra partida o al restaurar la galería.</t>
+  </si>
+  <si>
+    <t>separacion</t>
+  </si>
+  <si>
+    <t>Vida de cada soldado</t>
+  </si>
+  <si>
+    <t>Con la llamarada (15/s) arden casi al instante.</t>
+  </si>
+  <si>
+    <t>Puntos por soldado</t>
+  </si>
+  <si>
+    <t>puntos_soldado</t>
+  </si>
+  <si>
+    <t>Puntos al aniquilar el batallón</t>
+  </si>
+  <si>
+    <t>Además de los de cada soldado.</t>
+  </si>
+  <si>
+    <t>Velocidad de marcha</t>
+  </si>
+  <si>
+    <t>Aún sin uso: en la galería están quietos.</t>
+  </si>
+  <si>
+    <t>Daño que reciben</t>
+  </si>
+  <si>
+    <t>Radio extra de la llamarada</t>
+  </si>
+  <si>
+    <t>Se suma al cono de la llamarada (2 m + un 11 % de la distancia).</t>
+  </si>
+  <si>
+    <t>radio_llamas</t>
+  </si>
+  <si>
+    <t>Radio del disparo básico</t>
+  </si>
+  <si>
+    <t>Mueren los soldados a menos de esto del impacto.</t>
+  </si>
+  <si>
+    <t>radio_basico</t>
+  </si>
+  <si>
+    <t>Radio del disparo guiado</t>
+  </si>
+  <si>
+    <t>radio_guiado</t>
+  </si>
+  <si>
+    <t>Radio del rayo láser</t>
+  </si>
+  <si>
+    <t>radio_rayo</t>
+  </si>
+  <si>
+    <t>Flechas (sobre todo un efecto)</t>
+  </si>
+  <si>
+    <t>Disparan cuando pasas a menos de esto.</t>
+  </si>
+  <si>
+    <t>flechas_alcance</t>
+  </si>
+  <si>
+    <t>Flechas por andanada</t>
+  </si>
+  <si>
+    <t>flechas</t>
+  </si>
+  <si>
+    <t>Con el batallón entero (con menos soldados, menos flechas).</t>
+  </si>
+  <si>
+    <t>flechas_andanada</t>
+  </si>
+  <si>
+    <t>Pausa entre andanadas</t>
+  </si>
+  <si>
+    <t>flechas_pausa</t>
+  </si>
+  <si>
+    <t>Velocidad de las flechas</t>
+  </si>
+  <si>
+    <t>Con parábola.</t>
+  </si>
+  <si>
+    <t>flechas_vel</t>
+  </si>
+  <si>
+    <t>flechas_dispersion</t>
+  </si>
+  <si>
+    <t>Daño por flecha</t>
+  </si>
+  <si>
+    <t>Despreciable, a propósito (en hover justo encima, ~1 punto por segundo).</t>
+  </si>
+  <si>
+    <t>flechas_dano</t>
+  </si>
+  <si>
+    <t>Barco naval</t>
+  </si>
+  <si>
+    <t>Nueva (v29): barcos en el mar, como los dirigibles. Valores provisionales.</t>
+  </si>
+  <si>
+    <t>Como los dirigibles: un disparo guiado (60) lo hunde.</t>
+  </si>
+  <si>
+    <t>Puntos al hundirlo</t>
+  </si>
+  <si>
+    <t>Eslora</t>
+  </si>
+  <si>
+    <t>Cañones (solo por los costados, como los dirigibles)</t>
+  </si>
+  <si>
+    <t>Superdirigible</t>
+  </si>
+  <si>
+    <t>Nueva (v29): megaestructura del cielo con torretas que se destruyen aparte. Valores provisionales.</t>
+  </si>
+  <si>
+    <t>Núcleo (el casco)</t>
+  </si>
+  <si>
+    <t>Puntos de vida del núcleo</t>
+  </si>
+  <si>
+    <t>Se puede dañar aunque queden torretas; al caer, caen todas.</t>
+  </si>
+  <si>
+    <t>Jorge: 500 m como mínimo.</t>
+  </si>
+  <si>
+    <t>Altura mínima de vuelo</t>
+  </si>
+  <si>
+    <t>Sobre el suelo. La receta puede ponerlo más alto, nunca más bajo.</t>
+  </si>
+  <si>
+    <t>altura_min</t>
+  </si>
+  <si>
+    <t>Aún sin uso: en la galería está quieto.</t>
+  </si>
+  <si>
+    <t>Torretas (cañones y balistas sobre la cubierta)</t>
+  </si>
+  <si>
+    <t>Torretas por costado</t>
+  </si>
+  <si>
+    <t>torretas</t>
+  </si>
+  <si>
+    <t>Alternan cañón y balista; se fijan y se destruyen una a una (como mucho 6).</t>
+  </si>
+  <si>
+    <t>Vida de cada torreta</t>
+  </si>
+  <si>
+    <t>torreta_vida</t>
+  </si>
+  <si>
+    <t>Puntos por torreta</t>
+  </si>
+  <si>
+    <t>torreta_puntos</t>
+  </si>
+  <si>
+    <t>Tamaño de cada torreta</t>
+  </si>
+  <si>
+    <t>torreta_largo</t>
+  </si>
+  <si>
+    <t>Pausa entre disparos de cada torreta</t>
+  </si>
+  <si>
+    <t>Cada torreta dispara por su cuenta, solo hacia su costado.</t>
+  </si>
+  <si>
+    <t>torreta_cadencia</t>
+  </si>
+  <si>
+    <t>Como los cañones de los dirigibles.</t>
+  </si>
+  <si>
+    <t>Como los dirigibles: medido desde el eje del casco.</t>
+  </si>
+  <si>
+    <t>Elevación máxima</t>
+  </si>
+  <si>
+    <t>Sierpe</t>
+  </si>
+  <si>
+    <t>Nueva (v29): dragón serpiente gigante (minijefe) con hechiceros que la escudan. Valores provisionales.</t>
+  </si>
+  <si>
+    <t>Vida y tamaño</t>
+  </si>
+  <si>
+    <t>Solo recibe daño cuando cae su escudo.</t>
+  </si>
+  <si>
+    <t>Puntos al abatirla</t>
+  </si>
+  <si>
+    <t>Altura de vuelo</t>
+  </si>
+  <si>
+    <t>Sobre el suelo, si la receta no dice otra.</t>
+  </si>
+  <si>
+    <t>altura</t>
+  </si>
+  <si>
+    <t>Radio del círculo</t>
+  </si>
+  <si>
+    <t>En vuelo circular (en la galería, con el panel de pruebas).</t>
+  </si>
+  <si>
+    <t>radio_circulo</t>
+  </si>
+  <si>
+    <t>En vuelo circular.</t>
+  </si>
+  <si>
+    <t>Llamarada (si te pones delante de la cabeza)</t>
+  </si>
+  <si>
+    <t>Daño</t>
+  </si>
+  <si>
+    <t>Ángulo para empezarla</t>
+  </si>
+  <si>
+    <t>Te tiene que tener delante de la cabeza, a menos de este ángulo.</t>
+  </si>
+  <si>
+    <t>llamas_angulo</t>
+  </si>
+  <si>
+    <t>Duración</t>
+  </si>
+  <si>
+    <t>llamas_duracion</t>
+  </si>
+  <si>
+    <t>Pausa entre llamaradas</t>
+  </si>
+  <si>
+    <t>llamas_pausa</t>
+  </si>
+  <si>
+    <t>Bolas de fuego (como los dragones enemigos)</t>
+  </si>
+  <si>
+    <t>Hechiceros y escudo</t>
+  </si>
+  <si>
+    <t>Hechiceros en el lomo</t>
+  </si>
+  <si>
+    <t>hechiceros</t>
+  </si>
+  <si>
+    <t>Mientras quede alguno, el escudo la protege de todo daño (como mucho 3).</t>
+  </si>
+  <si>
+    <t>Vida de cada hechicero</t>
+  </si>
+  <si>
+    <t>hechicero_vida</t>
+  </si>
+  <si>
+    <t>Puntos por hechicero</t>
+  </si>
+  <si>
+    <t>hechicero_puntos</t>
+  </si>
+  <si>
     <t>Lance (aliado)</t>
   </si>
   <si>
@@ -782,13 +1165,7 @@
     <t>Armas (solo disparo básico y lanzallamas)</t>
   </si>
   <si>
-    <t>Pausa entre disparos (mínima)</t>
-  </si>
-  <si>
     <t>basico_pausa_min</t>
-  </si>
-  <si>
-    <t>Pausa entre disparos (máxima)</t>
   </si>
   <si>
     <t>basico_pausa_max</t>
@@ -1415,7 +1792,7 @@
   <sheetPr>
     <tabColor rgb="FFF2B84B"/>
   </sheetPr>
-  <dimension ref="B2:B21"/>
+  <dimension ref="B2:B22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1472,13 +1849,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+    <row r="13" ht="24" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1487,13 +1864,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+    <row r="16" ht="24" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1512,14 +1889,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+    <row r="21" ht="24" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1545,7 +1927,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1554,7 +1936,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1563,24 +1945,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1589,41 +1971,41 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <v>50</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B7" s="16">
         <v>200</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1632,121 +2014,121 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B9" s="16">
         <v>1</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B10" s="16">
         <v>2000</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B11" s="16">
         <v>0.3</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B12" s="16">
         <v>800</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B13" s="16">
         <v>1.72</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B14" s="16">
         <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B15" s="16">
         <v>50</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -1766,6 +2148,1690 @@
   <sheetPr>
     <tabColor rgb="FF5A6E8A"/>
   </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="16">
+        <v>40</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="16">
+        <v>80</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="16">
+        <v>11</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="16">
+        <v>20</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="16">
+        <v>3</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="16">
+        <v>1500</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="16">
+        <v>6</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B15" s="16">
+        <v>10</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="16">
+        <v>200</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A11:E11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF5A6E8A"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="16">
+        <v>80</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="16">
+        <v>300</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="16">
+        <v>1.6</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="16">
+        <v>2</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" s="16">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B11" s="16">
+        <v>150</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" s="16">
+        <v>5</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" s="16">
+        <v>3</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="16">
+        <v>12</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="16">
+        <v>5</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="16">
+        <v>400</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B20" s="16">
+        <v>40</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B21" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" s="16">
+        <v>75</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="16">
+        <v>4</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B24" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A18:E18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF5A6E8A"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="16">
+        <v>50</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="16">
+        <v>200</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="16">
+        <v>110</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="16">
+        <v>30</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="16">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="16">
+        <v>2000</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="16">
+        <v>800</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="16">
+        <v>1.72</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B17" s="16">
+        <v>35</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="16">
+        <v>70</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A11:E11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF5A6E8A"/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1500</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="16">
+        <v>2000</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" s="16">
+        <v>500</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B9" s="16">
+        <v>1500</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="16">
+        <v>60</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B12" s="16">
+        <v>6</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B13" s="16">
+        <v>50</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B14" s="16">
+        <v>100</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="16">
+        <v>24</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B16" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17" s="16">
+        <v>2</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="16">
+        <v>2000</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="16">
+        <v>800</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" s="16">
+        <v>1.72</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B21" s="16">
+        <v>35</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B22" s="16">
+        <v>70</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A11:E11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF5A6E8A"/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="16">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="16">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="16">
+        <v>500</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B10" s="16">
+        <v>2000</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B11" s="16">
+        <v>2500</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="16">
+        <v>150</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="16">
+        <v>40</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="16">
+        <v>900</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" s="16">
+        <v>25</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B17" s="16">
+        <v>4</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="B18" s="16">
+        <v>6</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" s="16">
+        <v>15</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="16">
+        <v>1500</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B22" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" s="16">
+        <v>2.4</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B25" s="16">
+        <v>3</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B26" s="16">
+        <v>60</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B27" s="16">
+        <v>300</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF5A6E8A"/>
+  </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1778,7 +3844,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>250</v>
+        <v>376</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1787,7 +3853,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>251</v>
+        <v>377</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1796,24 +3862,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>252</v>
+        <v>378</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1822,126 +3888,126 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="16">
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B7" s="16">
         <v>0.14</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>254</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B8" s="16">
         <v>0.26</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>256</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>257</v>
+        <v>381</v>
       </c>
       <c r="B9" s="16">
         <v>1000</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>258</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>259</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="16">
         <v>70</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>260</v>
+        <v>384</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="16">
         <v>200</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>261</v>
+        <v>385</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1950,121 +4016,121 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B14" s="16">
         <v>1100</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>262</v>
+        <v>386</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>263</v>
+        <v>387</v>
       </c>
       <c r="B15" s="16">
         <v>2000</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>264</v>
+        <v>388</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>265</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>266</v>
+        <v>390</v>
       </c>
       <c r="B16" s="16">
         <v>1000</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>267</v>
+        <v>391</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>268</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>269</v>
+        <v>393</v>
       </c>
       <c r="B17" s="16">
         <v>60</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>270</v>
+        <v>394</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>271</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>272</v>
+        <v>396</v>
       </c>
       <c r="B18" s="16">
         <v>600</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>273</v>
+        <v>397</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>274</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="B19" s="16">
         <v>5</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>276</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>277</v>
+        <v>401</v>
       </c>
       <c r="B20" s="16">
         <v>10</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>278</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -2094,7 +4160,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2105,7 +4171,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2116,30 +4182,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2150,10 +4216,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="11">
         <f>Base!B6</f>
@@ -2178,10 +4244,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>31</v>
       </c>
       <c r="C7" s="11">
         <f>Base!B7</f>
@@ -2206,10 +4272,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="11">
         <f>Base!B8</f>
@@ -2234,10 +4300,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="11">
         <f>Base!B9</f>
@@ -2262,10 +4328,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="11">
         <f>Base!B10</f>
@@ -2290,10 +4356,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="11">
         <f>Base!B11</f>
@@ -2318,10 +4384,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="11">
         <f>Base!B12</f>
@@ -2346,7 +4412,7 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2357,10 +4423,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="11">
         <f>Base!B14</f>
@@ -2385,10 +4451,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="11">
         <f>Base!B15</f>
@@ -2413,10 +4479,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="11">
         <f>Base!B16</f>
@@ -2441,10 +4507,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="11">
         <f>Base!B17</f>
@@ -2469,10 +4535,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="11">
         <f>Base!B18</f>
@@ -2497,7 +4563,7 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2508,10 +4574,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" s="11">
         <f>Base!B20</f>
@@ -2536,10 +4602,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" s="11">
         <f>Base!B21</f>
@@ -2564,10 +4630,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="11">
         <f>Base!B22</f>
@@ -2592,10 +4658,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" s="11">
         <f>Base!B23</f>
@@ -2620,7 +4686,7 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -2631,10 +4697,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="11">
         <f>Base!B25</f>
@@ -2659,10 +4725,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="11">
         <f>Base!B26</f>
@@ -2687,10 +4753,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" s="11">
         <f>Base!B27</f>
@@ -2715,10 +4781,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="11">
         <f>Base!B28</f>
@@ -2743,10 +4809,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" s="11">
         <f>Base!B29</f>
@@ -2771,7 +4837,7 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -2782,10 +4848,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" s="11">
         <f>Base!B31</f>
@@ -2810,10 +4876,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C32" s="11">
         <f>Base!B32</f>
@@ -2838,10 +4904,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C33" s="11">
         <f>Base!B33</f>
@@ -2866,10 +4932,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C34" s="11">
         <f>Base!B34</f>
@@ -2894,10 +4960,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="11">
         <f>Base!B35</f>
@@ -2922,7 +4988,7 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -2933,10 +4999,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C37" s="11">
         <f>Base!B37</f>
@@ -2961,10 +5027,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="C38" s="11">
         <f>Base!B38</f>
@@ -2989,10 +5055,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C39" s="11">
         <f>Base!B39</f>
@@ -3017,10 +5083,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C40" s="11">
         <f>Base!B40</f>
@@ -3045,10 +5111,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C41" s="11">
         <f>Base!B41</f>
@@ -3073,10 +5139,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C42" s="11">
         <f>Base!B42</f>
@@ -3101,10 +5167,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C43" s="11">
         <f>Base!B43</f>
@@ -3165,7 +5231,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3174,7 +5240,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3183,24 +5249,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3209,126 +5275,126 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <v>100</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="16">
         <v>50</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="16">
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="16">
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="16">
         <v>2</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="16">
         <v>5</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="16">
         <v>1</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3337,92 +5403,92 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16">
         <v>5</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="16">
         <v>20</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="16">
         <v>0.1</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="16">
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="16">
         <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -3431,75 +5497,75 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="16">
         <v>60</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="16">
         <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="16">
         <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="16">
         <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -3508,92 +5574,92 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="16">
         <v>15</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="16">
         <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="16">
         <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="16">
         <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="16">
         <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -3602,92 +5668,92 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="16">
         <v>50</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="16">
         <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="16">
         <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="16">
         <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="16">
         <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -3696,121 +5762,121 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="16">
         <v>600</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" s="16">
         <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" s="16">
         <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="16">
         <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="16">
         <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="16">
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="16">
         <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3848,7 +5914,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3859,7 +5925,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3870,30 +5936,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3904,14 +5970,14 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <f>Base!B6</f>
         <v>100</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="10">
         <f>Base!B6</f>
@@ -3922,22 +5988,22 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="16">
         <f>Base!B7</f>
         <v>50</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="10">
         <f>Base!B7</f>
@@ -3948,22 +6014,22 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="16">
         <f>Base!B8</f>
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="10">
         <f>Base!B8</f>
@@ -3974,22 +6040,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="16">
         <f>Base!B9</f>
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10">
         <f>Base!B9</f>
@@ -4000,22 +6066,22 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="16">
         <f>Base!B10</f>
         <v>2</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="10">
         <f>Base!B10</f>
@@ -4026,22 +6092,22 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="16">
         <f>Base!B11</f>
         <v>5</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="10">
         <f>Base!B11</f>
@@ -4052,22 +6118,22 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="16">
         <f>Base!B12</f>
         <v>1</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="10">
         <f>Base!B12</f>
@@ -4078,15 +6144,15 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -4097,14 +6163,14 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16">
         <f>Base!B14</f>
         <v>5</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="10">
         <f>Base!B14</f>
@@ -4115,22 +6181,22 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="16">
         <f>Base!B15</f>
         <v>20</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="10">
         <f>Base!B15</f>
@@ -4141,22 +6207,22 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="16">
         <f>Base!B16</f>
         <v>0.1</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="10">
         <f>Base!B16</f>
@@ -4167,22 +6233,22 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="16">
         <f>Base!B17</f>
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="10">
         <f>Base!B17</f>
@@ -4193,22 +6259,22 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="16">
         <f>Base!B18</f>
         <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="10">
         <f>Base!B18</f>
@@ -4219,15 +6285,15 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -4238,14 +6304,14 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="16">
         <f>Base!B20</f>
         <v>60</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="10">
         <f>Base!B20</f>
@@ -4256,22 +6322,22 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="16">
         <f>Base!B21</f>
         <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="10">
         <f>Base!B21</f>
@@ -4282,22 +6348,22 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
         <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
@@ -4308,22 +6374,22 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
         <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
@@ -4334,15 +6400,15 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -4353,14 +6419,14 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="16">
         <f>Base!B25</f>
         <v>15</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="10">
         <f>Base!B25</f>
@@ -4371,22 +6437,22 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
         <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
@@ -4397,22 +6463,22 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
         <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
@@ -4423,22 +6489,22 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
         <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
@@ -4449,22 +6515,22 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
         <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
@@ -4475,15 +6541,15 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -4494,14 +6560,14 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="16">
         <f>Base!B31</f>
         <v>50</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="10">
         <f>Base!B31</f>
@@ -4512,22 +6578,22 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
         <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
@@ -4538,22 +6604,22 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
         <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
@@ -4564,22 +6630,22 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
         <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
@@ -4590,22 +6656,22 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
         <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
@@ -4616,15 +6682,15 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -4635,14 +6701,14 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="16">
         <f>Base!B37</f>
         <v>600</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="10">
         <f>Base!B37</f>
@@ -4653,22 +6719,22 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
         <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
@@ -4679,22 +6745,22 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
         <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
@@ -4705,22 +6771,22 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
         <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
@@ -4731,22 +6797,22 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
         <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
@@ -4757,22 +6823,22 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="16">
         <f>Base!B42</f>
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -4783,22 +6849,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
         <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
@@ -4809,10 +6875,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -4855,7 +6921,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4866,7 +6932,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -4877,30 +6943,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -4911,14 +6977,14 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <f>Base!B6</f>
         <v>100</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="10">
         <f>Base!B6</f>
@@ -4929,22 +6995,22 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="16">
         <f>Base!B7</f>
         <v>50</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="10">
         <f>Base!B7</f>
@@ -4955,22 +7021,22 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="16">
         <f>Base!B8</f>
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="10">
         <f>Base!B8</f>
@@ -4981,22 +7047,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="16">
         <f>Base!B9</f>
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10">
         <f>Base!B9</f>
@@ -5007,22 +7073,22 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="16">
         <f>Base!B10</f>
         <v>2</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="10">
         <f>Base!B10</f>
@@ -5033,22 +7099,22 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="16">
         <f>Base!B11</f>
         <v>5</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="10">
         <f>Base!B11</f>
@@ -5059,22 +7125,22 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="16">
         <f>Base!B12</f>
         <v>1</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="10">
         <f>Base!B12</f>
@@ -5085,15 +7151,15 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -5104,14 +7170,14 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16">
         <f>Base!B14</f>
         <v>5</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="10">
         <f>Base!B14</f>
@@ -5122,22 +7188,22 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="16">
         <f>Base!B15</f>
         <v>20</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="10">
         <f>Base!B15</f>
@@ -5148,22 +7214,22 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="16">
         <f>Base!B16</f>
         <v>0.1</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="10">
         <f>Base!B16</f>
@@ -5174,22 +7240,22 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="16">
         <f>Base!B17</f>
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="10">
         <f>Base!B17</f>
@@ -5200,22 +7266,22 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="16">
         <f>Base!B18</f>
         <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="10">
         <f>Base!B18</f>
@@ -5226,15 +7292,15 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -5245,14 +7311,14 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="16">
         <f>Base!B20</f>
         <v>60</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="10">
         <f>Base!B20</f>
@@ -5263,22 +7329,22 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="16">
         <f>Base!B21</f>
         <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="10">
         <f>Base!B21</f>
@@ -5289,22 +7355,22 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
         <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
@@ -5315,22 +7381,22 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
         <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
@@ -5341,15 +7407,15 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -5360,14 +7426,14 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="16">
         <f>Base!B25</f>
         <v>15</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="10">
         <f>Base!B25</f>
@@ -5378,22 +7444,22 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
         <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
@@ -5404,22 +7470,22 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
         <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
@@ -5430,22 +7496,22 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
         <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
@@ -5456,22 +7522,22 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
         <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
@@ -5482,15 +7548,15 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -5501,14 +7567,14 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="16">
         <f>Base!B31</f>
         <v>50</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="10">
         <f>Base!B31</f>
@@ -5519,22 +7585,22 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
         <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
@@ -5545,22 +7611,22 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
         <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
@@ -5571,22 +7637,22 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
         <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
@@ -5597,22 +7663,22 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
         <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
@@ -5623,15 +7689,15 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -5642,14 +7708,14 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="16">
         <f>Base!B37</f>
         <v>600</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="10">
         <f>Base!B37</f>
@@ -5660,22 +7726,22 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
         <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
@@ -5686,22 +7752,22 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
         <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
@@ -5712,22 +7778,22 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
         <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
@@ -5738,22 +7804,22 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
         <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
@@ -5764,22 +7830,22 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="16">
         <f>Base!B42</f>
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -5790,22 +7856,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
         <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
@@ -5816,10 +7882,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5862,7 +7928,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5873,7 +7939,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5884,30 +7950,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -5918,14 +7984,14 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <f>Base!B6</f>
         <v>100</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="10">
         <f>Base!B6</f>
@@ -5936,22 +8002,22 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="16">
         <f>Base!B7</f>
         <v>50</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="10">
         <f>Base!B7</f>
@@ -5962,22 +8028,22 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="16">
         <f>Base!B8</f>
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="10">
         <f>Base!B8</f>
@@ -5988,22 +8054,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="16">
         <f>Base!B9</f>
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10">
         <f>Base!B9</f>
@@ -6014,22 +8080,22 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="16">
         <f>Base!B10</f>
         <v>2</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="10">
         <f>Base!B10</f>
@@ -6040,22 +8106,22 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="16">
         <f>Base!B11</f>
         <v>5</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="10">
         <f>Base!B11</f>
@@ -6066,22 +8132,22 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="16">
         <f>Base!B12</f>
         <v>1</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="10">
         <f>Base!B12</f>
@@ -6092,15 +8158,15 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -6111,14 +8177,14 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16">
         <f>Base!B14</f>
         <v>5</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="10">
         <f>Base!B14</f>
@@ -6129,22 +8195,22 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="16">
         <f>Base!B15</f>
         <v>20</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="10">
         <f>Base!B15</f>
@@ -6155,22 +8221,22 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="16">
         <f>Base!B16</f>
         <v>0.1</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="10">
         <f>Base!B16</f>
@@ -6181,22 +8247,22 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="16">
         <f>Base!B17</f>
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="10">
         <f>Base!B17</f>
@@ -6207,22 +8273,22 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="16">
         <f>Base!B18</f>
         <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="10">
         <f>Base!B18</f>
@@ -6233,15 +8299,15 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -6252,14 +8318,14 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="16">
         <f>Base!B20</f>
         <v>60</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="10">
         <f>Base!B20</f>
@@ -6270,22 +8336,22 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="16">
         <f>Base!B21</f>
         <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="10">
         <f>Base!B21</f>
@@ -6296,22 +8362,22 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
         <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
@@ -6322,22 +8388,22 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
         <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
@@ -6348,15 +8414,15 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6367,14 +8433,14 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="16">
         <f>Base!B25</f>
         <v>15</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="10">
         <f>Base!B25</f>
@@ -6385,22 +8451,22 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
         <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
@@ -6411,22 +8477,22 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
         <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
@@ -6437,22 +8503,22 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
         <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
@@ -6463,22 +8529,22 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
         <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
@@ -6489,15 +8555,15 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -6508,14 +8574,14 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="16">
         <f>Base!B31</f>
         <v>50</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="10">
         <f>Base!B31</f>
@@ -6526,22 +8592,22 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
         <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
@@ -6552,22 +8618,22 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
         <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
@@ -6578,22 +8644,22 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
         <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
@@ -6604,22 +8670,22 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
         <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
@@ -6630,15 +8696,15 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -6649,14 +8715,14 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="16">
         <f>Base!B37</f>
         <v>600</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="10">
         <f>Base!B37</f>
@@ -6667,22 +8733,22 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
         <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
@@ -6693,22 +8759,22 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
         <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
@@ -6719,22 +8785,22 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
         <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
@@ -6745,22 +8811,22 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
         <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
@@ -6771,22 +8837,22 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="16">
         <f>Base!B42</f>
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -6797,22 +8863,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
         <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
@@ -6823,10 +8889,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -6869,7 +8935,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -6880,7 +8946,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -6891,30 +8957,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -6925,14 +8991,14 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <f>Base!B6</f>
         <v>100</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="10">
         <f>Base!B6</f>
@@ -6943,22 +9009,22 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="16">
         <f>Base!B7</f>
         <v>50</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="10">
         <f>Base!B7</f>
@@ -6969,22 +9035,22 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="16">
         <f>Base!B8</f>
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="10">
         <f>Base!B8</f>
@@ -6995,22 +9061,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="16">
         <f>Base!B9</f>
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10">
         <f>Base!B9</f>
@@ -7021,22 +9087,22 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="16">
         <f>Base!B10</f>
         <v>2</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="10">
         <f>Base!B10</f>
@@ -7047,22 +9113,22 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="16">
         <f>Base!B11</f>
         <v>5</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="10">
         <f>Base!B11</f>
@@ -7073,22 +9139,22 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="16">
         <f>Base!B12</f>
         <v>1</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="10">
         <f>Base!B12</f>
@@ -7099,15 +9165,15 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -7118,14 +9184,14 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16">
         <f>Base!B14</f>
         <v>5</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="10">
         <f>Base!B14</f>
@@ -7136,22 +9202,22 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="16">
         <f>Base!B15</f>
         <v>20</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="10">
         <f>Base!B15</f>
@@ -7162,22 +9228,22 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="16">
         <f>Base!B16</f>
         <v>0.1</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="10">
         <f>Base!B16</f>
@@ -7188,22 +9254,22 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="16">
         <f>Base!B17</f>
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="10">
         <f>Base!B17</f>
@@ -7214,22 +9280,22 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="16">
         <f>Base!B18</f>
         <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="10">
         <f>Base!B18</f>
@@ -7240,15 +9306,15 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -7259,14 +9325,14 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="16">
         <f>Base!B20</f>
         <v>60</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="10">
         <f>Base!B20</f>
@@ -7277,22 +9343,22 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="16">
         <f>Base!B21</f>
         <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="10">
         <f>Base!B21</f>
@@ -7303,22 +9369,22 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="16">
         <f>Base!B22</f>
         <v>3000</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="10">
         <f>Base!B22</f>
@@ -7329,22 +9395,22 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
         <v>3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
@@ -7355,15 +9421,15 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -7374,14 +9440,14 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="16">
         <f>Base!B25</f>
         <v>15</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="10">
         <f>Base!B25</f>
@@ -7392,22 +9458,22 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="16">
         <f>Base!B26</f>
         <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="10">
         <f>Base!B26</f>
@@ -7418,22 +9484,22 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="16">
         <f>Base!B27</f>
         <v>5</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="10">
         <f>Base!B27</f>
@@ -7444,22 +9510,22 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="16">
         <f>Base!B28</f>
         <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="10">
         <f>Base!B28</f>
@@ -7470,22 +9536,22 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="16">
         <f>Base!B29</f>
         <v>4</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="10">
         <f>Base!B29</f>
@@ -7496,15 +9562,15 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -7515,14 +9581,14 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="16">
         <f>Base!B31</f>
         <v>50</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="10">
         <f>Base!B31</f>
@@ -7533,22 +9599,22 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="16">
         <f>Base!B32</f>
         <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="10">
         <f>Base!B32</f>
@@ -7559,22 +9625,22 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="16">
         <f>Base!B33</f>
         <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D33" s="10">
         <f>Base!B33</f>
@@ -7585,22 +9651,22 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="16">
         <f>Base!B34</f>
         <v>0.5</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="10">
         <f>Base!B34</f>
@@ -7611,22 +9677,22 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="16">
         <f>Base!B35</f>
         <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="10">
         <f>Base!B35</f>
@@ -7637,15 +9703,15 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -7656,14 +9722,14 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="16">
         <f>Base!B37</f>
         <v>600</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="10">
         <f>Base!B37</f>
@@ -7674,22 +9740,22 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" s="16">
         <f>Base!B38</f>
         <v>1000</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="10">
         <f>Base!B38</f>
@@ -7700,22 +9766,22 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" s="16">
         <f>Base!B39</f>
         <v>10</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" s="10">
         <f>Base!B39</f>
@@ -7726,22 +9792,22 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="16">
         <f>Base!B40</f>
         <v>3</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="10">
         <f>Base!B40</f>
@@ -7752,22 +9818,22 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="16">
         <f>Base!B41</f>
         <v>2</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D41" s="10">
         <f>Base!B41</f>
@@ -7778,22 +9844,22 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="16">
         <f>Base!B42</f>
         <v>2</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="10">
         <f>Base!B42</f>
@@ -7804,22 +9870,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="16">
         <f>Base!B43</f>
         <v>110</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="10">
         <f>Base!B43</f>
@@ -7830,10 +9896,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -7874,7 +9940,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7883,7 +9949,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -7892,24 +9958,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -7918,109 +9984,109 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <v>70</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="16">
         <v>500</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16">
         <v>130</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B9" s="16">
         <v>2000</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B10" s="16">
         <v>3500</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B11" s="16">
         <v>300</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -8029,58 +10095,58 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" s="16">
         <v>1800</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" s="16">
         <v>10</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" s="16">
         <v>18</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -8089,92 +10155,92 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B17" s="16">
         <v>10</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B18" s="16">
         <v>1000</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B19" s="16">
         <v>1.7</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B20" s="16">
         <v>2.9</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B21" s="16">
         <v>2.2</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -8183,143 +10249,143 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B23" s="16">
         <v>30</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="16">
         <v>4</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B25" s="16">
         <v>500</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B26" s="16">
         <v>2000</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B27" s="16">
         <v>60</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B28" s="16">
         <v>20</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B29" s="16">
         <v>1152</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B30" s="16">
         <v>30</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -8328,36 +10394,36 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B32" s="16">
         <v>25</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B33" s="16">
         <v>50</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -8392,7 +10458,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8401,7 +10467,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -8410,24 +10476,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -8436,58 +10502,58 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <v>60</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B7" s="16">
         <v>100</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -8496,138 +10562,138 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B10" s="16">
         <v>3</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B11" s="16">
         <v>1500</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B12" s="16">
         <v>5</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B13" s="16">
         <v>0.12</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B14" s="16">
         <v>2.2</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B15" s="16">
         <v>3.6</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B16" s="16">
         <v>1100</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B17" s="16">
         <v>2</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -1003,7 +1003,7 @@
     <t>Se puede dañar aunque queden torretas; al caer, caen todas.</t>
   </si>
   <si>
-    <t>Jorge: 500 m como mínimo.</t>
+    <t>Jorge: 500 m como mínimo (v29) y luego el doble (v30). Las torretas no cambian de tamaño: quedan más separadas.</t>
   </si>
   <si>
     <t>Altura mínima de vuelo</t>
@@ -1093,7 +1093,7 @@
     <t>Radio del círculo</t>
   </si>
   <si>
-    <t>En vuelo circular (en la galería, con el panel de pruebas).</t>
+    <t>En vuelo circular: su patrulla (en la galería, sobre todo el campo).</t>
   </si>
   <si>
     <t>radio_circulo</t>
@@ -3157,7 +3157,7 @@
         <v>318</v>
       </c>
       <c r="B8" s="16">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>54</v>
@@ -3552,7 +3552,7 @@
         <v>354</v>
       </c>
       <c r="B11" s="16">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>54</v>

--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -370,7 +370,7 @@
     <t>guiado_alcance</t>
   </si>
   <si>
-    <t>Segundos con la mira en el círculo rojo hasta que sale.</t>
+    <t>Segundos con la mira en el círculo rojo hasta que sale (v31: 2, antes 3).</t>
   </si>
   <si>
     <t>guiado_fijado</t>
@@ -4665,23 +4665,23 @@
       </c>
       <c r="C23" s="11">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="12">
         <f>'Alientormenta'!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="12">
         <f>'Abrasanubes'!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="12">
         <f>'Ventoscuro'!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="12">
         <f>'Fulgor'!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5551,7 +5551,7 @@
         <v>55</v>
       </c>
       <c r="B23" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>35</v>
@@ -6386,14 +6386,14 @@
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>
@@ -7393,14 +7393,14 @@
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>
@@ -9407,14 +9407,14 @@
       </c>
       <c r="B23" s="16">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="10">
         <f>Base!B23</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="19">
         <f>IF(D23=0,"",B23/D23-1)</f>

--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="416">
   <si>
     <t>Sky Apex · Stats de las unidades</t>
   </si>
@@ -268,6 +268,21 @@
     <t>Radio de giro</t>
   </si>
   <si>
+    <t>Esquiva (A / D)</t>
+  </si>
+  <si>
+    <t>Distancia de la esquiva</t>
+  </si>
+  <si>
+    <t>Duración de la esquiva</t>
+  </si>
+  <si>
+    <t>Espera entre esquivas</t>
+  </si>
+  <si>
+    <t>Despiste de guiadas</t>
+  </si>
+  <si>
     <t>Valores base de los dragones del jugador. Cada dragón los copia salvo los que cambies en su pestaña.</t>
   </si>
   <si>
@@ -476,6 +491,30 @@
   </si>
   <si>
     <t>giro_radio</t>
+  </si>
+  <si>
+    <t>Lo que se desplaza de lado, sin cambiar el rumbo (v32). Con mucho más, en 3ª persona el dragón se sale de la pantalla mientras la cámara se queda atrás.</t>
+  </si>
+  <si>
+    <t>esquiva_distancia</t>
+  </si>
+  <si>
+    <t>Segundos que dura el desplazamiento y el tonel de 360°.</t>
+  </si>
+  <si>
+    <t>esquiva_duracion</t>
+  </si>
+  <si>
+    <t>Segundos desde que acaba una hasta que se puede hacer la siguiente.</t>
+  </si>
+  <si>
+    <t>esquiva_recarga</t>
+  </si>
+  <si>
+    <t>Al esquivar, las bolas guiadas enemigas a menos de esto pierden el blanco y siguen rectas (0 = ninguna).</t>
+  </si>
+  <si>
+    <t>esquiva_guiadas</t>
   </si>
   <si>
     <t>Dragón del jugador. «Valor» sigue a la Base hasta que escribas otro número (su variación, en naranja).</t>
@@ -1927,7 +1966,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1936,7 +1975,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1948,21 +1987,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1980,15 +2019,15 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B7" s="16">
         <v>200</v>
@@ -1997,7 +2036,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>32</v>
@@ -2005,7 +2044,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2014,7 +2053,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B9" s="16">
         <v>1</v>
@@ -2023,32 +2062,32 @@
         <v>32</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B10" s="16">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B11" s="16">
         <v>0.3</v>
@@ -2057,78 +2096,78 @@
         <v>35</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B12" s="16">
         <v>800</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B13" s="16">
         <v>1.72</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B14" s="16">
         <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B15" s="16">
         <v>50</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2160,7 +2199,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2169,7 +2208,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2181,21 +2220,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2213,15 +2252,15 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B7" s="16">
         <v>80</v>
@@ -2230,7 +2269,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>32</v>
@@ -2238,7 +2277,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2247,7 +2286,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B9" s="16">
         <v>11</v>
@@ -2256,15 +2295,15 @@
         <v>54</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B10" s="16">
         <v>20</v>
@@ -2273,15 +2312,15 @@
         <v>73</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2290,7 +2329,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B12" s="16">
         <v>3</v>
@@ -2299,32 +2338,32 @@
         <v>32</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B13" s="16">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B14" s="16">
         <v>6</v>
@@ -2333,15 +2372,15 @@
         <v>35</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B15" s="16">
         <v>10</v>
@@ -2350,44 +2389,44 @@
         <v>35</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B16" s="16">
         <v>200</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B17" s="16">
         <v>2.5</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -2420,7 +2459,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2429,7 +2468,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2441,21 +2480,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2464,41 +2503,41 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="B6" s="16">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="B7" s="16">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B8" s="16">
         <v>1.6</v>
@@ -2507,15 +2546,15 @@
         <v>54</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B9" s="16">
         <v>2</v>
@@ -2524,15 +2563,15 @@
         <v>32</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B10" s="16">
         <v>2</v>
@@ -2541,15 +2580,15 @@
         <v>32</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B11" s="16">
         <v>150</v>
@@ -2558,7 +2597,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>32</v>
@@ -2566,7 +2605,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B12" s="16">
         <v>5</v>
@@ -2575,15 +2614,15 @@
         <v>73</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2592,7 +2631,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="B14" s="16">
         <v>3</v>
@@ -2601,15 +2640,15 @@
         <v>54</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B15" s="16">
         <v>2.5</v>
@@ -2618,15 +2657,15 @@
         <v>54</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B16" s="16">
         <v>12</v>
@@ -2635,15 +2674,15 @@
         <v>54</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="B17" s="16">
         <v>5</v>
@@ -2652,15 +2691,15 @@
         <v>54</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2669,7 +2708,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B19" s="16">
         <v>400</v>
@@ -2678,32 +2717,32 @@
         <v>54</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B20" s="16">
         <v>40</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B21" s="16">
         <v>2.5</v>
@@ -2712,49 +2751,49 @@
         <v>35</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B22" s="16">
         <v>75</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B23" s="16">
         <v>4</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B24" s="16">
         <v>0.1</v>
@@ -2763,10 +2802,10 @@
         <v>32</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -2799,7 +2838,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2808,7 +2847,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2820,21 +2859,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2852,15 +2891,15 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B7" s="16">
         <v>200</v>
@@ -2869,7 +2908,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>32</v>
@@ -2877,7 +2916,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2886,7 +2925,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B9" s="16">
         <v>110</v>
@@ -2895,15 +2934,15 @@
         <v>54</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B10" s="16">
         <v>30</v>
@@ -2912,15 +2951,15 @@
         <v>73</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2929,7 +2968,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B12" s="16">
         <v>2</v>
@@ -2938,32 +2977,32 @@
         <v>32</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B13" s="16">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B14" s="16">
         <v>0.3</v>
@@ -2972,78 +3011,78 @@
         <v>35</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B15" s="16">
         <v>800</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B16" s="16">
         <v>1.72</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B17" s="16">
         <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B18" s="16">
         <v>70</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3076,7 +3115,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3085,7 +3124,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3097,21 +3136,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3120,7 +3159,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B6" s="16">
         <v>1500</v>
@@ -3129,15 +3168,15 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B7" s="16">
         <v>2000</v>
@@ -3146,7 +3185,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>32</v>
@@ -3154,7 +3193,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B8" s="16">
         <v>1000</v>
@@ -3163,15 +3202,15 @@
         <v>54</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B9" s="16">
         <v>1500</v>
@@ -3180,15 +3219,15 @@
         <v>54</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B10" s="16">
         <v>60</v>
@@ -3197,15 +3236,15 @@
         <v>73</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3214,24 +3253,24 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B12" s="16">
         <v>6</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B13" s="16">
         <v>50</v>
@@ -3240,15 +3279,15 @@
         <v>32</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B14" s="16">
         <v>100</v>
@@ -3257,15 +3296,15 @@
         <v>32</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B15" s="16">
         <v>24</v>
@@ -3274,15 +3313,15 @@
         <v>54</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="B16" s="16">
         <v>1.5</v>
@@ -3291,15 +3330,15 @@
         <v>35</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B17" s="16">
         <v>2</v>
@@ -3308,15 +3347,15 @@
         <v>32</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B18" s="16">
         <v>2000</v>
@@ -3325,78 +3364,78 @@
         <v>54</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B19" s="16">
         <v>800</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B20" s="16">
         <v>1.72</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B21" s="16">
         <v>35</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B22" s="16">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3428,7 +3467,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3437,7 +3476,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3449,21 +3488,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3475,21 +3514,21 @@
         <v>31</v>
       </c>
       <c r="B6" s="16">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="B7" s="16">
         <v>5000</v>
@@ -3498,7 +3537,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>32</v>
@@ -3506,7 +3545,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B8" s="16">
         <v>500</v>
@@ -3515,10 +3554,10 @@
         <v>54</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3532,7 +3571,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B10" s="16">
         <v>2000</v>
@@ -3541,15 +3580,15 @@
         <v>54</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="B11" s="16">
         <v>3500</v>
@@ -3558,32 +3597,32 @@
         <v>54</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B12" s="16">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3592,7 +3631,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B14" s="16">
         <v>40</v>
@@ -3601,15 +3640,15 @@
         <v>37</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B15" s="16">
         <v>900</v>
@@ -3618,32 +3657,32 @@
         <v>54</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B16" s="16">
         <v>25</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="B17" s="16">
         <v>4</v>
@@ -3652,15 +3691,15 @@
         <v>35</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="B18" s="16">
         <v>6</v>
@@ -3669,15 +3708,15 @@
         <v>35</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -3686,7 +3725,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B20" s="16">
         <v>15</v>
@@ -3695,15 +3734,15 @@
         <v>32</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B21" s="16">
         <v>1500</v>
@@ -3712,15 +3751,15 @@
         <v>54</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B22" s="16">
         <v>1.2</v>
@@ -3729,15 +3768,15 @@
         <v>35</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B23" s="16">
         <v>2.4</v>
@@ -3746,15 +3785,15 @@
         <v>35</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -3763,24 +3802,24 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="B25" s="16">
         <v>3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B26" s="16">
         <v>60</v>
@@ -3789,15 +3828,15 @@
         <v>32</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="B27" s="16">
         <v>300</v>
@@ -3806,10 +3845,10 @@
         <v>32</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3844,7 +3883,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3853,7 +3892,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3865,21 +3904,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3897,15 +3936,15 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B7" s="16">
         <v>0.14</v>
@@ -3914,15 +3953,15 @@
         <v>35</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B8" s="16">
         <v>0.26</v>
@@ -3931,15 +3970,15 @@
         <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="B9" s="16">
         <v>1000</v>
@@ -3948,27 +3987,27 @@
         <v>54</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3982,10 +4021,10 @@
         <v>37</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3999,15 +4038,15 @@
         <v>54</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -4025,15 +4064,15 @@
         <v>73</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B15" s="16">
         <v>2000</v>
@@ -4042,15 +4081,15 @@
         <v>54</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="B16" s="16">
         <v>1000</v>
@@ -4059,15 +4098,15 @@
         <v>54</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B17" s="16">
         <v>60</v>
@@ -4076,15 +4115,15 @@
         <v>70</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="B18" s="16">
         <v>600</v>
@@ -4093,15 +4132,15 @@
         <v>54</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B19" s="16">
         <v>5</v>
@@ -4110,15 +4149,15 @@
         <v>35</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="B20" s="16">
         <v>10</v>
@@ -4127,10 +4166,10 @@
         <v>35</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -4150,7 +4189,7 @@
   <sheetPr>
     <tabColor rgb="FF7A6A5A"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -5193,8 +5232,131 @@
         <v>110</v>
       </c>
     </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="11">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="D45" s="12">
+        <f>'Alientormenta'!B45</f>
+        <v>25</v>
+      </c>
+      <c r="E45" s="12">
+        <f>'Abrasanubes'!B45</f>
+        <v>25</v>
+      </c>
+      <c r="F45" s="12">
+        <f>'Ventoscuro'!B45</f>
+        <v>25</v>
+      </c>
+      <c r="G45" s="12">
+        <f>'Fulgor'!B45</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="11">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="D46" s="12">
+        <f>'Alientormenta'!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="E46" s="12">
+        <f>'Abrasanubes'!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="F46" s="12">
+        <f>'Ventoscuro'!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="G46" s="12">
+        <f>'Fulgor'!B46</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="11">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="D47" s="12">
+        <f>'Alientormenta'!B47</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="12">
+        <f>'Abrasanubes'!B47</f>
+        <v>1</v>
+      </c>
+      <c r="F47" s="12">
+        <f>'Ventoscuro'!B47</f>
+        <v>1</v>
+      </c>
+      <c r="G47" s="12">
+        <f>'Fulgor'!B47</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="11">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="D48" s="12">
+        <f>'Alientormenta'!B48</f>
+        <v>400</v>
+      </c>
+      <c r="E48" s="12">
+        <f>'Abrasanubes'!B48</f>
+        <v>400</v>
+      </c>
+      <c r="F48" s="12">
+        <f>'Ventoscuro'!B48</f>
+        <v>400</v>
+      </c>
+      <c r="G48" s="12">
+        <f>'Fulgor'!B48</f>
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
@@ -5203,8 +5365,9 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:G43">
+  <conditionalFormatting sqref="D5:G48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(ISNUMBER($C5),D5&lt;&gt;$C5)</formula>
     </cfRule>
@@ -5219,7 +5382,7 @@
   <sheetPr>
     <tabColor rgb="FFF2B84B"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -5240,7 +5403,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5252,16 +5415,16 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5284,10 +5447,10 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5301,10 +5464,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5318,10 +5481,10 @@
         <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5335,10 +5498,10 @@
         <v>37</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5352,10 +5515,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5369,10 +5532,10 @@
         <v>35</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5386,10 +5549,10 @@
         <v>39</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5412,10 +5575,10 @@
         <v>32</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,10 +5592,10 @@
         <v>45</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5446,10 +5609,10 @@
         <v>35</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5463,10 +5626,10 @@
         <v>35</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5480,10 +5643,10 @@
         <v>49</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5506,10 +5669,10 @@
         <v>32</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5523,10 +5686,10 @@
         <v>45</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5540,10 +5703,10 @@
         <v>54</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5557,10 +5720,10 @@
         <v>35</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5583,10 +5746,10 @@
         <v>37</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5600,10 +5763,10 @@
         <v>54</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5617,10 +5780,10 @@
         <v>35</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5634,10 +5797,10 @@
         <v>35</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5651,10 +5814,10 @@
         <v>35</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5677,10 +5840,10 @@
         <v>37</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5694,10 +5857,10 @@
         <v>35</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5711,10 +5874,10 @@
         <v>66</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5728,10 +5891,10 @@
         <v>68</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5745,10 +5908,10 @@
         <v>70</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5771,10 +5934,10 @@
         <v>73</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -5788,10 +5951,10 @@
         <v>73</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -5805,10 +5968,10 @@
         <v>35</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -5822,10 +5985,10 @@
         <v>35</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -5839,10 +6002,10 @@
         <v>35</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -5856,10 +6019,10 @@
         <v>68</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -5873,14 +6036,91 @@
         <v>54</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="16">
+        <v>25</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="16">
+        <v>1</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="16">
+        <v>400</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:E5"/>
@@ -5889,6 +6129,7 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5900,7 +6141,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -5925,7 +6166,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5939,7 +6180,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
@@ -5948,13 +6189,13 @@
         <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5988,10 +6229,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6014,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6040,10 +6281,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6066,10 +6307,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6092,10 +6333,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6118,10 +6359,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6144,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6181,10 +6422,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6207,10 +6448,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6233,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6259,10 +6500,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6285,10 +6526,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6322,10 +6563,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6348,10 +6589,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -6374,10 +6615,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -6400,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6437,10 +6678,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -6463,10 +6704,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -6489,10 +6730,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -6515,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -6541,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6578,10 +6819,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -6604,10 +6845,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -6630,10 +6871,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -6656,10 +6897,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -6682,10 +6923,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6719,10 +6960,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -6745,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -6771,10 +7012,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -6797,10 +7038,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -6823,10 +7064,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -6849,10 +7090,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -6875,14 +7116,129 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="16">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="10">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="E45" s="19">
+        <f>IF(D45=0,"",B45/D45-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="16">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="10">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="E46" s="19">
+        <f>IF(D46=0,"",B46/D46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="16">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="10">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="19">
+        <f>IF(D47=0,"",B47/D47-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="16">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="10">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="E48" s="19">
+        <f>IF(D48=0,"",B48/D48-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
@@ -6891,8 +7247,9 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B43">
+  <conditionalFormatting sqref="B5:B48">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -6907,7 +7264,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -6932,7 +7289,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -6946,7 +7303,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
@@ -6955,13 +7312,13 @@
         <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6995,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7021,10 +7378,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7047,10 +7404,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7073,10 +7430,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7099,10 +7456,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7125,10 +7482,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7151,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7188,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7214,10 +7571,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7240,10 +7597,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7266,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7292,10 +7649,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7329,10 +7686,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7355,10 +7712,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -7381,10 +7738,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -7407,10 +7764,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7444,10 +7801,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -7470,10 +7827,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -7496,10 +7853,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -7522,10 +7879,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -7548,10 +7905,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7585,10 +7942,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -7611,10 +7968,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -7637,10 +7994,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -7663,10 +8020,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -7689,10 +8046,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7726,10 +8083,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -7752,10 +8109,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -7778,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -7804,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -7830,10 +8187,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -7856,10 +8213,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -7882,14 +8239,129 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="16">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="10">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="E45" s="19">
+        <f>IF(D45=0,"",B45/D45-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="16">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="10">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="E46" s="19">
+        <f>IF(D46=0,"",B46/D46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="16">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="10">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="19">
+        <f>IF(D47=0,"",B47/D47-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="16">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="10">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="E48" s="19">
+        <f>IF(D48=0,"",B48/D48-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
@@ -7898,8 +8370,9 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B43">
+  <conditionalFormatting sqref="B5:B48">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -7914,7 +8387,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -7939,7 +8412,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -7953,7 +8426,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
@@ -7962,13 +8435,13 @@
         <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8002,10 +8475,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8028,10 +8501,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8054,10 +8527,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8080,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8106,10 +8579,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8132,10 +8605,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8158,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8195,10 +8668,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8221,10 +8694,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8247,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8273,10 +8746,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,10 +8772,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8336,10 +8809,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8362,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8388,10 +8861,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -8414,10 +8887,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8451,10 +8924,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -8477,10 +8950,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -8503,10 +8976,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -8529,10 +9002,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -8555,10 +9028,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8592,10 +9065,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -8618,10 +9091,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,10 +9117,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -8670,10 +9143,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -8696,10 +9169,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8733,10 +9206,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -8759,10 +9232,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -8785,10 +9258,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -8811,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -8837,10 +9310,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -8863,10 +9336,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -8889,14 +9362,129 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="16">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="10">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="E45" s="19">
+        <f>IF(D45=0,"",B45/D45-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="16">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="10">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="E46" s="19">
+        <f>IF(D46=0,"",B46/D46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="16">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="10">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="19">
+        <f>IF(D47=0,"",B47/D47-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="16">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="10">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="E48" s="19">
+        <f>IF(D48=0,"",B48/D48-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
@@ -8905,8 +9493,9 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B43">
+  <conditionalFormatting sqref="B5:B48">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -8921,7 +9510,7 @@
   <sheetPr>
     <tabColor rgb="FFC0501A"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -8946,7 +9535,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -8960,7 +9549,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
@@ -8969,13 +9558,13 @@
         <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9009,10 +9598,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,10 +9624,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9061,10 +9650,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9087,10 +9676,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9113,10 +9702,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9139,10 +9728,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -9165,10 +9754,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9202,10 +9791,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9228,10 +9817,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9254,10 +9843,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9280,10 +9869,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -9306,10 +9895,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9343,10 +9932,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9369,10 +9958,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -9395,10 +9984,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -9421,10 +10010,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9458,10 +10047,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -9484,10 +10073,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -9510,10 +10099,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -9536,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -9562,10 +10151,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9599,10 +10188,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -9625,10 +10214,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -9651,10 +10240,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -9677,10 +10266,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -9703,10 +10292,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9740,10 +10329,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -9766,10 +10355,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -9792,10 +10381,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -9818,10 +10407,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -9844,10 +10433,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -9870,10 +10459,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -9896,14 +10485,129 @@
         <v>0</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="16">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="10">
+        <f>Base!B45</f>
+        <v>25</v>
+      </c>
+      <c r="E45" s="19">
+        <f>IF(D45=0,"",B45/D45-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="16">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="10">
+        <f>Base!B46</f>
+        <v>0.6</v>
+      </c>
+      <c r="E46" s="19">
+        <f>IF(D46=0,"",B46/D46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="16">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="10">
+        <f>Base!B47</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="19">
+        <f>IF(D47=0,"",B47/D47-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="16">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="10">
+        <f>Base!B48</f>
+        <v>400</v>
+      </c>
+      <c r="E48" s="19">
+        <f>IF(D48=0,"",B48/D48-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
@@ -9912,8 +10616,9 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B43">
+  <conditionalFormatting sqref="B5:B48">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(ISNUMBER(D5),B5&lt;&gt;D5)</formula>
     </cfRule>
@@ -9940,7 +10645,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -9949,7 +10654,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -9961,21 +10666,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -9993,10 +10698,10 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -10010,10 +10715,10 @@
         <v>73</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -10027,15 +10732,15 @@
         <v>54</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B9" s="16">
         <v>2000</v>
@@ -10044,15 +10749,15 @@
         <v>54</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B10" s="16">
         <v>3500</v>
@@ -10061,15 +10766,15 @@
         <v>54</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B11" s="16">
         <v>300</v>
@@ -10078,7 +10783,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>32</v>
@@ -10086,7 +10791,7 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -10095,7 +10800,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B13" s="16">
         <v>1800</v>
@@ -10104,15 +10809,15 @@
         <v>54</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B14" s="16">
         <v>10</v>
@@ -10121,15 +10826,15 @@
         <v>35</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B15" s="16">
         <v>18</v>
@@ -10138,15 +10843,15 @@
         <v>35</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -10155,7 +10860,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B17" s="16">
         <v>10</v>
@@ -10164,15 +10869,15 @@
         <v>32</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B18" s="16">
         <v>1000</v>
@@ -10181,15 +10886,15 @@
         <v>54</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B19" s="16">
         <v>1.7</v>
@@ -10198,15 +10903,15 @@
         <v>35</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B20" s="16">
         <v>2.9</v>
@@ -10215,32 +10920,32 @@
         <v>35</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B21" s="16">
         <v>2.2</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -10249,7 +10954,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B23" s="16">
         <v>30</v>
@@ -10258,10 +10963,10 @@
         <v>32</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -10275,15 +10980,15 @@
         <v>35</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B25" s="16">
         <v>500</v>
@@ -10292,15 +10997,15 @@
         <v>54</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B26" s="16">
         <v>2000</v>
@@ -10309,15 +11014,15 @@
         <v>54</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B27" s="16">
         <v>60</v>
@@ -10326,15 +11031,15 @@
         <v>35</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B28" s="16">
         <v>20</v>
@@ -10343,15 +11048,15 @@
         <v>35</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B29" s="16">
         <v>1152</v>
@@ -10360,32 +11065,32 @@
         <v>73</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B30" s="16">
         <v>30</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -10394,7 +11099,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B32" s="16">
         <v>25</v>
@@ -10403,15 +11108,15 @@
         <v>32</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B33" s="16">
         <v>50</v>
@@ -10420,10 +11125,10 @@
         <v>32</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -10458,7 +11163,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10467,7 +11172,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -10479,21 +11184,21 @@
         <v>23</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -10511,15 +11216,15 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B7" s="16">
         <v>100</v>
@@ -10528,7 +11233,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>32</v>
@@ -10536,24 +11241,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -10562,7 +11267,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B10" s="16">
         <v>3</v>
@@ -10571,32 +11276,32 @@
         <v>32</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B11" s="16">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B12" s="16">
         <v>5</v>
@@ -10605,15 +11310,15 @@
         <v>45</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B13" s="16">
         <v>0.12</v>
@@ -10622,15 +11327,15 @@
         <v>35</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B14" s="16">
         <v>2.2</v>
@@ -10639,15 +11344,15 @@
         <v>35</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B15" s="16">
         <v>3.6</v>
@@ -10656,44 +11361,44 @@
         <v>35</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B16" s="16">
         <v>1100</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B17" s="16">
         <v>2</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -5252,23 +5252,23 @@
       </c>
       <c r="C45" s="11">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D45" s="12">
         <f>'Alientormenta'!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E45" s="12">
         <f>'Abrasanubes'!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F45" s="12">
         <f>'Ventoscuro'!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G45" s="12">
         <f>'Fulgor'!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -5280,23 +5280,23 @@
       </c>
       <c r="C46" s="11">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="D46" s="12">
         <f>'Alientormenta'!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="12">
         <f>'Abrasanubes'!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="F46" s="12">
         <f>'Ventoscuro'!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="G46" s="12">
         <f>'Fulgor'!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -6056,7 +6056,7 @@
         <v>81</v>
       </c>
       <c r="B45" s="16">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>54</v>
@@ -6073,7 +6073,7 @@
         <v>82</v>
       </c>
       <c r="B46" s="16">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>35</v>
@@ -7139,14 +7139,14 @@
       </c>
       <c r="B45" s="16">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D45" s="10">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E45" s="19">
         <f>IF(D45=0,"",B45/D45-1)</f>
@@ -7165,14 +7165,14 @@
       </c>
       <c r="B46" s="16">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="10">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="19">
         <f>IF(D46=0,"",B46/D46-1)</f>
@@ -8262,14 +8262,14 @@
       </c>
       <c r="B45" s="16">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D45" s="10">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E45" s="19">
         <f>IF(D45=0,"",B45/D45-1)</f>
@@ -8288,14 +8288,14 @@
       </c>
       <c r="B46" s="16">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="10">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="19">
         <f>IF(D46=0,"",B46/D46-1)</f>
@@ -9385,14 +9385,14 @@
       </c>
       <c r="B45" s="16">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D45" s="10">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E45" s="19">
         <f>IF(D45=0,"",B45/D45-1)</f>
@@ -9411,14 +9411,14 @@
       </c>
       <c r="B46" s="16">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="10">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="19">
         <f>IF(D46=0,"",B46/D46-1)</f>
@@ -10508,14 +10508,14 @@
       </c>
       <c r="B45" s="16">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D45" s="10">
         <f>Base!B45</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E45" s="19">
         <f>IF(D45=0,"",B45/D45-1)</f>
@@ -10534,14 +10534,14 @@
       </c>
       <c r="B46" s="16">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="10">
         <f>Base!B46</f>
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="19">
         <f>IF(D46=0,"",B46/D46-1)</f>

--- a/datos/sky_apex_stats.xlsx
+++ b/datos/sky_apex_stats.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="453">
   <si>
     <t>Sky Apex · Stats de las unidades</t>
   </si>
@@ -1105,6 +1105,69 @@
     <t>Elevación máxima</t>
   </si>
   <si>
+    <t>Rayo de la proa (v34, Capítulo 1)</t>
+  </si>
+  <si>
+    <t>Primer rayo</t>
+  </si>
+  <si>
+    <t>Desde que empieza el combate (se cierra el portal). Petición de Jorge: a los 60 s.</t>
+  </si>
+  <si>
+    <t>rayo_espera</t>
+  </si>
+  <si>
+    <t>Carga del rayo</t>
+  </si>
+  <si>
+    <t>La esfera de energía crece en la proa; los aliados avisan.</t>
+  </si>
+  <si>
+    <t>rayo_carga</t>
+  </si>
+  <si>
+    <t>Duración del rayo</t>
+  </si>
+  <si>
+    <t>Pausa entre rayos</t>
+  </si>
+  <si>
+    <t>Desde que acaba uno hasta que empieza a cargar el siguiente.</t>
+  </si>
+  <si>
+    <t>rayo_repetir</t>
+  </si>
+  <si>
+    <t>Daño si te cruzas</t>
+  </si>
+  <si>
+    <t>Nunca apunta al jugador: dispara a los aliados (que no reciben daño).</t>
+  </si>
+  <si>
+    <t>Radio de daño</t>
+  </si>
+  <si>
+    <t>rayo_radio</t>
+  </si>
+  <si>
+    <t>Ancho del rayo</t>
+  </si>
+  <si>
+    <t>Aspecto: el halo; el núcleo blanco es un 40 % y el aura, el doble.</t>
+  </si>
+  <si>
+    <t>rayo_ancho</t>
+  </si>
+  <si>
+    <t>Giro siguiendo al blanco</t>
+  </si>
+  <si>
+    <t>Lo que tarda en seguir al aliado: le da tiempo a apartarse (el rayo pasa rozándole).</t>
+  </si>
+  <si>
+    <t>rayo_giro</t>
+  </si>
+  <si>
     <t>Sierpe</t>
   </si>
   <si>
@@ -1274,6 +1337,54 @@
   </si>
   <si>
     <t>blanco_max</t>
+  </si>
+  <si>
+    <t>Escolta (v34: los compañeros del Capítulo 1)</t>
+  </si>
+  <si>
+    <t>Radio de las vueltas a tu alrededor</t>
+  </si>
+  <si>
+    <t>Casi no atacan: te dan vueltas y te defienden de vez en cuando.</t>
+  </si>
+  <si>
+    <t>escolta_radio</t>
+  </si>
+  <si>
+    <t>Tiempo persiguiendo a un dragón</t>
+  </si>
+  <si>
+    <t>Cuando persiguen a uno que va a por ti.</t>
+  </si>
+  <si>
+    <t>escolta_persecucion</t>
+  </si>
+  <si>
+    <t>Pausa entre persecuciones</t>
+  </si>
+  <si>
+    <t>Cada aliado (con algo de azar).</t>
+  </si>
+  <si>
+    <t>escolta_pausa</t>
+  </si>
+  <si>
+    <t>Su daño</t>
+  </si>
+  <si>
+    <t>Del daño normal del aliado.</t>
+  </si>
+  <si>
+    <t>escolta_dano</t>
+  </si>
+  <si>
+    <t>Vida mínima en que dejan a un enemigo</t>
+  </si>
+  <si>
+    <t>No rematan: los derribos son tuyos.</t>
+  </si>
+  <si>
+    <t>escolta_vida_min</t>
   </si>
 </sst>
 </file>
@@ -3103,7 +3214,7 @@
   <sheetPr>
     <tabColor rgb="FF5A6E8A"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3438,12 +3549,175 @@
         <v>263</v>
       </c>
     </row>
+    <row r="23" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" s="16">
+        <v>60</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B25" s="16">
+        <v>10</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B26" s="16">
+        <v>4</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B27" s="16">
+        <v>45</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B28" s="16">
+        <v>30</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B29" s="16">
+        <v>30</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B30" s="16">
+        <v>70</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="16">
+        <v>12000</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B32" s="16">
+        <v>2</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>379</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A23:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3467,7 +3741,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3476,7 +3750,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3502,7 +3776,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3520,7 +3794,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>90</v>
@@ -3528,7 +3802,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="B7" s="16">
         <v>5000</v>
@@ -3571,7 +3845,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="B10" s="16">
         <v>2000</v>
@@ -3580,15 +3854,15 @@
         <v>54</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="B11" s="16">
         <v>3500</v>
@@ -3597,10 +3871,10 @@
         <v>54</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3614,7 +3888,7 @@
         <v>73</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>169</v>
@@ -3622,7 +3896,7 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3631,7 +3905,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B14" s="16">
         <v>40</v>
@@ -3665,7 +3939,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="B16" s="16">
         <v>25</v>
@@ -3674,15 +3948,15 @@
         <v>246</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="B17" s="16">
         <v>4</v>
@@ -3694,12 +3968,12 @@
         <v>168</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="B18" s="16">
         <v>6</v>
@@ -3711,12 +3985,12 @@
         <v>168</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -3725,7 +3999,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B20" s="16">
         <v>15</v>
@@ -3793,7 +4067,7 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -3802,24 +4076,24 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="B25" s="16">
         <v>3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="B26" s="16">
         <v>60</v>
@@ -3831,12 +4105,12 @@
         <v>168</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="B27" s="16">
         <v>300</v>
@@ -3848,7 +4122,7 @@
         <v>168</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -3871,7 +4145,7 @@
   <sheetPr>
     <tabColor rgb="FF5A6E8A"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3883,7 +4157,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3892,7 +4166,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3918,7 +4192,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3956,7 +4230,7 @@
         <v>168</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3973,12 +4247,12 @@
         <v>168</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="B9" s="16">
         <v>1000</v>
@@ -3990,7 +4264,7 @@
         <v>168</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4007,7 +4281,7 @@
         <v>168</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4021,7 +4295,7 @@
         <v>37</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>122</v>
@@ -4046,7 +4320,7 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -4064,7 +4338,7 @@
         <v>73</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>142</v>
@@ -4072,7 +4346,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="B15" s="16">
         <v>2000</v>
@@ -4081,15 +4355,15 @@
         <v>54</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="B16" s="16">
         <v>1000</v>
@@ -4098,15 +4372,15 @@
         <v>54</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="B17" s="16">
         <v>60</v>
@@ -4115,15 +4389,15 @@
         <v>70</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="B18" s="16">
         <v>600</v>
@@ -4132,15 +4406,15 @@
         <v>54</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="B19" s="16">
         <v>5</v>
@@ -4152,12 +4426,12 @@
         <v>168</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="B20" s="16">
         <v>10</v>
@@ -4169,15 +4443,110 @@
         <v>168</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>415</v>
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B22" s="16">
+        <v>550</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="B23" s="16">
+        <v>5</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="B24" s="16">
+        <v>14</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25" s="16">
+        <v>25</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B26" s="16">
+        <v>40</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
